--- a/data/reports/TEC22_Data/B2_final_predictions_comparison.xlsx
+++ b/data/reports/TEC22_Data/B2_final_predictions_comparison.xlsx
@@ -503,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.505414247512817</v>
+        <v>-1.507258296012878</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9482550621032715</v>
+        <v>1.025321245193481</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.531839966773987</v>
+        <v>-1.519555568695068</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7048072814941406</v>
+        <v>0.8044549226760864</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.616744756698608</v>
+        <v>-1.610749244689941</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9026831984519958</v>
+        <v>0.991117537021637</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.415926814079285</v>
+        <v>-1.403019070625305</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.463950902223587</v>
+        <v>0.5783096551895142</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.332113146781921</v>
+        <v>-1.283248662948608</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.004121422767639</v>
+        <v>1.105843067169189</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.252555131912231</v>
+        <v>-1.197530508041382</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7326017022132874</v>
+        <v>0.806309700012207</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.241902947425842</v>
+        <v>-1.184786558151245</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.546051621437073</v>
+        <v>1.595441222190857</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3585195541381836</v>
+        <v>-0.4520705938339233</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.069485902786255</v>
+        <v>2.14750862121582</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.328497588634491</v>
+        <v>-0.4442669749259949</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.174667835235596</v>
+        <v>2.039299726486206</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3356443643569946</v>
+        <v>-0.4274004995822906</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.78462553024292</v>
+        <v>1.676832914352417</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3494941890239716</v>
+        <v>-0.4510971903800964</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.133933782577515</v>
+        <v>2.045265436172485</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.4198358654975891</v>
+        <v>-0.5330066084861755</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.405094146728516</v>
+        <v>2.288878440856934</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.402734249830246</v>
+        <v>-0.5110474824905396</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1.950469732284546</v>
+        <v>1.827998042106628</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3842735886573792</v>
+        <v>-0.5151006579399109</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.002244710922241</v>
+        <v>1.885879635810852</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1443773508071899</v>
+        <v>0.0007957308553159237</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.681236267089844</v>
+        <v>1.57631254196167</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1348053961992264</v>
+        <v>-0.01504645869135857</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.618212461471558</v>
+        <v>1.505748510360718</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1350130289793015</v>
+        <v>-0.04065250232815742</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.891412615776062</v>
+        <v>1.788768649101257</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.13411545753479</v>
+        <v>-0.01237665303051472</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.560160636901855</v>
+        <v>1.458411931991577</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1285913437604904</v>
+        <v>-0.03131569549441338</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.67329728603363</v>
+        <v>1.600017309188843</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1621126979589462</v>
+        <v>0.02521103248000145</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.016507983207703</v>
+        <v>0.9177400469779968</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1906944513320923</v>
+        <v>0.0787583664059639</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1.003296971321106</v>
+        <v>0.8739262819290161</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.177960216999054</v>
+        <v>0.09445604681968689</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.615407347679138</v>
+        <v>1.479663133621216</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.228650689125061</v>
+        <v>0.1464801579713821</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9776051640510559</v>
+        <v>0.8633168935775757</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5721923112869263</v>
+        <v>0.5718590617179871</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.687022864818573</v>
+        <v>-0.7519617080688477</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.04793740436434746</v>
+        <v>0.02199834212660789</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1511,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.480063438415527</v>
+        <v>-1.418078660964966</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.040216363966465</v>
+        <v>-0.0239874292165041</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1552,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4561322331428528</v>
+        <v>0.514674961566925</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.165299266576767</v>
+        <v>0.1217682063579559</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1593,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8570895195007324</v>
+        <v>0.8775262832641602</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.141832172870636</v>
+        <v>0.1225728243589401</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.4298639297485352</v>
+        <v>-0.3626236915588379</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1610888987779617</v>
+        <v>0.1080762892961502</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2216526418924332</v>
+        <v>0.2745660543441772</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1347006559371948</v>
+        <v>0.08449450135231018</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2724113166332245</v>
+        <v>0.2901721894741058</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1107272058725357</v>
+        <v>0.04879119619727135</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3161816298961639</v>
+        <v>0.3463284969329834</v>
       </c>
       <c r="L32" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1056830808520317</v>
+        <v>0.02006818354129791</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4549826383590698</v>
+        <v>0.5106121301651001</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.09411138296127319</v>
+        <v>-0.007997265085577965</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3654961585998535</v>
+        <v>0.3771247863769531</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.08781871199607849</v>
+        <v>-0.02492060139775276</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1880,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.370426744222641</v>
+        <v>0.402353048324585</v>
       </c>
       <c r="L35" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1206175312399864</v>
+        <v>0.0668613463640213</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.5089201927185059</v>
+        <v>-0.4513961970806122</v>
       </c>
       <c r="L36" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1410761028528214</v>
+        <v>0.1021045446395874</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1962,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.0007377688307315111</v>
+        <v>0.05142535269260406</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1282308846712112</v>
+        <v>0.02639969438314438</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.4468358755111694</v>
+        <v>0.4767184853553772</v>
       </c>
       <c r="L38" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4680474400520325</v>
+        <v>0.3678495287895203</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2044,10 +2044,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8477367758750916</v>
+        <v>0.9035325646400452</v>
       </c>
       <c r="L39" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5784761905670166</v>
+        <v>0.5036921501159668</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2085,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.3092900514602661</v>
+        <v>-0.259088546037674</v>
       </c>
       <c r="L40" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.561195433139801</v>
+        <v>0.4650399684906006</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2717794179916382</v>
+        <v>0.31769660115242</v>
       </c>
       <c r="L41" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5273746252059937</v>
+        <v>0.4278698563575745</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.4471010863780975</v>
+        <v>0.4679215550422668</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4658536911010742</v>
+        <v>0.3604919016361237</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2208,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4843389391899109</v>
+        <v>0.4886069595813751</v>
       </c>
       <c r="L43" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.492196649312973</v>
+        <v>0.4173192083835602</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2249,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.5821404457092285</v>
+        <v>-0.4886018931865692</v>
       </c>
       <c r="L44" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4488402009010315</v>
+        <v>0.3604239225387573</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5087167620658875</v>
+        <v>0.5044524073600769</v>
       </c>
       <c r="L45" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.464275449514389</v>
+        <v>0.3690476715564728</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2331,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1079000011086464</v>
+        <v>0.1353858560323715</v>
       </c>
       <c r="L46" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5259882807731628</v>
+        <v>0.4161312282085419</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2372,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.08347886055707932</v>
+        <v>-0.03708448261022568</v>
       </c>
       <c r="L47" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5148752927780151</v>
+        <v>0.3947464227676392</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2413,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2524868547916412</v>
+        <v>0.2917254567146301</v>
       </c>
       <c r="L48" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5079324841499329</v>
+        <v>0.3787252902984619</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2454,10 +2454,10 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4801627993583679</v>
+        <v>0.5106433033943176</v>
       </c>
       <c r="L49" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5759685039520264</v>
+        <v>0.4428098797798157</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1396090686321259</v>
+        <v>-0.08263418823480606</v>
       </c>
       <c r="L50" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6042688488960266</v>
+        <v>0.4895933270454407</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2536,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.4518274664878845</v>
+        <v>-0.364960789680481</v>
       </c>
       <c r="L51" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5659722685813904</v>
+        <v>0.4676096737384796</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2577,10 +2577,10 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.3088482022285461</v>
+        <v>-0.2584083080291748</v>
       </c>
       <c r="L52" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6033287644386292</v>
+        <v>0.5222913026809692</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2618,10 +2618,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.0894535779953</v>
+        <v>-0.9957094192504883</v>
       </c>
       <c r="L53" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3985173404216766</v>
+        <v>0.3671641945838928</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3376302421092987</v>
+        <v>0.3927279114723206</v>
       </c>
       <c r="L54" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6088815331459045</v>
+        <v>0.4855882525444031</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2700,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3877496421337128</v>
+        <v>0.4079687297344208</v>
       </c>
       <c r="L55" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4077704548835754</v>
+        <v>0.3716127276420593</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2833479046821594</v>
+        <v>0.3508070707321167</v>
       </c>
       <c r="L56" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4160529375076294</v>
+        <v>0.3518302142620087</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5738126635551453</v>
+        <v>0.6005841493606567</v>
       </c>
       <c r="L57" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.424502819776535</v>
+        <v>0.3556859195232391</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2823,10 +2823,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3672411143779755</v>
+        <v>0.3960760831832886</v>
       </c>
       <c r="L58" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.615201473236084</v>
+        <v>0.4908654391765594</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.04696428775787354</v>
+        <v>0.07033757865428925</v>
       </c>
       <c r="L59" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4610491096973419</v>
+        <v>0.3808857202529907</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2905,10 +2905,10 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.01901878416538239</v>
+        <v>0.01420252025127411</v>
       </c>
       <c r="L60" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2780211567878723</v>
+        <v>0.2274413704872131</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2946,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4507190883159637</v>
+        <v>0.4857290685176849</v>
       </c>
       <c r="L61" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.509684145450592</v>
+        <v>0.4770731925964355</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8705218434333801</v>
+        <v>0.8311400413513184</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5058465003967285</v>
+        <v>0.4458993077278137</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2205523103475571</v>
+        <v>0.1877285689115524</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6784994602203369</v>
+        <v>0.5888864398002625</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2153014838695526</v>
+        <v>0.2175334244966507</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3180851340293884</v>
+        <v>0.2826806902885437</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.08804784715175629</v>
+        <v>-0.1228745654225349</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.204388901591301</v>
+        <v>0.1780244112014771</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3565179705619812</v>
+        <v>0.353028804063797</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02990424819290638</v>
+        <v>0.01516741141676903</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2912169694900513</v>
+        <v>0.2638311088085175</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2780211567878723</v>
+        <v>0.2274413704872131</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7805678248405457</v>
+        <v>0.7460066080093384</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.394237607717514</v>
+        <v>0.3417956233024597</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.5525113344192505</v>
+        <v>0.4809013307094574</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4276616275310516</v>
+        <v>0.3815886080265045</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1.086873888969421</v>
+        <v>1.079559564590454</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2738191187381744</v>
+        <v>0.2037657201290131</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.1901191920042038</v>
+        <v>-0.1657246351242065</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2765793204307556</v>
+        <v>0.2205461710691452</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2599614858627319</v>
+        <v>0.2364084273576736</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2585743963718414</v>
+        <v>0.2189720720052719</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1849569827318192</v>
+        <v>0.1859750598669052</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.136717289686203</v>
+        <v>0.124521017074585</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.008072047494351864</v>
+        <v>-0.01844462566077709</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.20498126745224</v>
+        <v>0.1753922998905182</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2530796825885773</v>
+        <v>0.2421718537807465</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.141657367348671</v>
+        <v>0.1243032142519951</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02237026020884514</v>
+        <v>0.03492189571261406</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1829758882522583</v>
+        <v>0.1666427701711655</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3213804364204407</v>
+        <v>0.3172064125537872</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5093525648117065</v>
+        <v>0.4527062177658081</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.01767983473837376</v>
+        <v>-0.02248783223330975</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3420632183551788</v>
+        <v>0.2899472415447235</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.1136790886521339</v>
+        <v>-0.1142466589808464</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2971618175506592</v>
+        <v>0.260907918214798</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.07646648585796356</v>
+        <v>0.08663016557693481</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1972856074571609</v>
+        <v>0.1703907251358032</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.1754975765943527</v>
+        <v>-0.1641914695501328</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1877416372299194</v>
+        <v>0.1476080119609833</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2956858277320862</v>
+        <v>0.2827472686767578</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1775391697883606</v>
+        <v>0.149766594171524</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3126526474952698</v>
+        <v>0.2954680919647217</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.07835381478071213</v>
+        <v>0.05263902992010117</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.09233728796243668</v>
+        <v>-0.08177661895751953</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.02117136865854263</v>
+        <v>-0.0009101519244723022</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.3560561835765839</v>
+        <v>-0.3417676687240601</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1795673668384552</v>
+        <v>0.148757129907608</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.1260292828083038</v>
+        <v>-0.1585191488265991</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1795673668384552</v>
+        <v>0.148757129907608</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1037226915359497</v>
+        <v>0.09875886142253876</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.361208975315094</v>
+        <v>0.3022564947605133</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1094479709863663</v>
+        <v>0.08917650580406189</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3477482497692108</v>
+        <v>0.2970139980316162</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1193736717104912</v>
+        <v>0.1285916864871979</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2964899241924286</v>
+        <v>0.2659927308559418</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1470985412597656</v>
+        <v>0.1324300467967987</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.332217276096344</v>
+        <v>0.2920457124710083</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.2748483121395111</v>
+        <v>0.2593081295490265</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3755960166454315</v>
+        <v>0.3517081439495087</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.9952383041381836</v>
+        <v>-0.8780971169471741</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3810963332653046</v>
+        <v>0.3591855466365814</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.2867719233036041</v>
+        <v>0.286223292350769</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.461646556854248</v>
+        <v>0.4390591382980347</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.431238204240799</v>
+        <v>0.4294322431087494</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4197902381420135</v>
+        <v>0.4002144634723663</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.197308212518692</v>
+        <v>0.1946838945150375</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2969870269298553</v>
+        <v>0.2812260389328003</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.00554310716688633</v>
+        <v>0.03503068163990974</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2722867727279663</v>
+        <v>0.2489759922027588</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.2385529726743698</v>
+        <v>0.2227085381746292</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4202131330966949</v>
+        <v>0.3907236754894257</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.5939269661903381</v>
+        <v>0.5598306655883789</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0.461646556854248</v>
+        <v>0.4390591382980347</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.3335395157337189</v>
+        <v>0.3247912228107452</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3261051774024963</v>
+        <v>0.3105390965938568</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.3826530873775482</v>
+        <v>-0.3392259478569031</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2567857205867767</v>
+        <v>0.2443978786468506</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.194876492023468</v>
+        <v>-0.1564558148384094</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.06860718876123428</v>
+        <v>0.07576925307512283</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>-0.3785153031349182</v>
+        <v>-0.332452654838562</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3487434089183807</v>
+        <v>0.3359309136867523</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0.5676657557487488</v>
+        <v>0.5902566909790039</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.4020988345146179</v>
+        <v>0.3808048069477081</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0242000725120306</v>
+        <v>0.06491103023290634</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4210346341133118</v>
+        <v>0.3931067883968353</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>-0.02511133812367916</v>
+        <v>0.01430009119212627</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2098393887281418</v>
+        <v>0.2033475786447525</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -4791,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>-0.513570249080658</v>
+        <v>-0.4522269368171692</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2482044100761414</v>
+        <v>0.2383726239204407</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>0.08471596240997314</v>
+        <v>0.1150195971131325</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.07723983377218246</v>
+        <v>0.04720554500818253</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0.2623998522758484</v>
+        <v>0.2490997761487961</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2266897708177567</v>
+        <v>0.2127164006233215</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>-1.240702390670776</v>
+        <v>-1.188729643821716</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.01410465966910124</v>
+        <v>-0.03755772858858109</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>-0.4681141376495361</v>
+        <v>-0.43694207072258</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.4646833539009094</v>
+        <v>-0.4388670027256012</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>-0.8066514134407043</v>
+        <v>-0.7369498014450073</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.5806278586387634</v>
+        <v>-0.5673802495002747</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0.161521315574646</v>
+        <v>0.1881997883319855</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.4820603430271149</v>
+        <v>-0.4994640052318573</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2528258264064789</v>
+        <v>0.2657261192798615</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.3728144764900208</v>
+        <v>-0.3705262541770935</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>0.1626371443271637</v>
+        <v>0.190461739897728</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.360923707485199</v>
+        <v>-0.3525842130184174</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -5160,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>-0.006659341510385275</v>
+        <v>0.001117072300985456</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.3104880154132843</v>
+        <v>-0.308197021484375</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2013270258903503</v>
+        <v>0.2072803378105164</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.2481810003519058</v>
+        <v>-0.2535033524036407</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1265301406383514</v>
+        <v>0.1387604027986526</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.2656338214874268</v>
+        <v>-0.272540420293808</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0.114281453192234</v>
+        <v>0.1437118053436279</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.3135881125926971</v>
+        <v>-0.3105489313602448</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>-0.307592511177063</v>
+        <v>-0.2671183049678802</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3389363586902618</v>
+        <v>-0.3338532447814941</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0.1490758657455444</v>
+        <v>0.1797103732824326</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.3069042563438416</v>
+        <v>-0.3063251376152039</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0.1365175843238831</v>
+        <v>0.14820796251297</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.4193593263626099</v>
+        <v>-0.4019091427326202</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>0.04811318218708038</v>
+        <v>0.05886899679899216</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.5335151553153992</v>
+        <v>-0.5250374674797058</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>0.2118735313415527</v>
+        <v>0.2333372384309769</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.628348171710968</v>
+        <v>-0.5936648845672607</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0.186879962682724</v>
+        <v>0.1827743947505951</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.553327739238739</v>
+        <v>-0.5346775650978088</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>0.3348120152950287</v>
+        <v>0.3509689271450043</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.5447368025779724</v>
+        <v>-0.5362618565559387</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>0.05225812271237373</v>
+        <v>0.05849142745137215</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.548883855342865</v>
+        <v>-0.5270078182220459</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>-0.002722030971199274</v>
+        <v>0.03064285591244698</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.64449143409729</v>
+        <v>-0.6099690198898315</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0.09573154151439667</v>
+        <v>0.128355398774147</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.695531964302063</v>
+        <v>-0.6560477614402771</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>-0.3786784410476685</v>
+        <v>-0.3250101208686829</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.3725453615188599</v>
+        <v>-0.3743190765380859</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0.5264884233474731</v>
+        <v>0.5269747376441956</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.5120577812194824</v>
+        <v>-0.50612473487854</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -5816,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.8332176208496094</v>
+        <v>-0.7516465783119202</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.259612113237381</v>
+        <v>-0.2574857473373413</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1721337288618088</v>
+        <v>0.1869187504053116</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.4232908487319946</v>
+        <v>-0.413614958524704</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.1515541672706604</v>
+        <v>-0.1088173389434814</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.527849555015564</v>
+        <v>-0.5104493498802185</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0.1641313582658768</v>
+        <v>0.1903579235076904</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.3801808953285217</v>
+        <v>-0.3735162913799286</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0.5742669105529785</v>
+        <v>0.5881383419036865</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2634419202804565</v>
+        <v>-0.2651175856590271</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0.2870142161846161</v>
+        <v>0.304771363735199</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.1410817056894302</v>
+        <v>-0.1619544476270676</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0.2706571221351624</v>
+        <v>0.3094973564147949</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.1106754690408707</v>
+        <v>-0.1170114502310753</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -6103,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0.1283255070447922</v>
+        <v>0.1734148114919662</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.1385365277528763</v>
+        <v>-0.1464123725891113</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>-0.08294661343097687</v>
+        <v>-0.01663400419056416</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.1810804754495621</v>
+        <v>-0.1716847866773605</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -6185,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>-0.2431501150131226</v>
+        <v>-0.2034711688756943</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.1385365277528763</v>
+        <v>-0.1464123725891113</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>-0.03733725473284721</v>
+        <v>-0.001718050334602594</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.1335969120264053</v>
+        <v>-0.1528262048959732</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>-0.4024310708045959</v>
+        <v>-0.3605692684650421</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6284,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.1330207288265228</v>
+        <v>-0.1363417059183121</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>-0.1412935554981232</v>
+        <v>-0.09663234651088715</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.1772136837244034</v>
+        <v>-0.17634417116642</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>-0.4241305589675903</v>
+        <v>-0.4009875655174255</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.2450263351202011</v>
+        <v>-0.2536799907684326</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>-0.208665519952774</v>
+        <v>-0.1636396795511246</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.1433143019676208</v>
+        <v>-0.1464123725891113</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0.3312326073646545</v>
+        <v>0.361905962228775</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0.04935935884714127</v>
+        <v>0.03322646394371986</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0.4784064888954163</v>
+        <v>0.5016351938247681</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0.01546366605907679</v>
+        <v>-0.004306657239794731</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0.1032170355319977</v>
+        <v>0.1312482059001923</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.009162270464003086</v>
+        <v>-0.01406103279441595</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0.1055389791727066</v>
+        <v>0.1359298974275589</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1745431274175644</v>
+        <v>0.153400331735611</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0.3568201661109924</v>
+        <v>0.3842870593070984</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2291480302810669</v>
+        <v>0.2018401920795441</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0.09076302498579025</v>
+        <v>0.1137275323271751</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0.169884666800499</v>
+        <v>0.1342938840389252</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -6677,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>0.0187990739941597</v>
+        <v>0.03763875365257263</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1761116683483124</v>
+        <v>0.1519325971603394</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0.0986882820725441</v>
+        <v>0.1112513616681099</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0.194238692522049</v>
+        <v>0.1796956211328506</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0.2705699503421783</v>
+        <v>0.2558496594429016</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>0.3157378733158112</v>
+        <v>0.2809526324272156</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1808585077524185</v>
+        <v>0.1840247958898544</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0.3010669946670532</v>
+        <v>0.257355123758316</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>-0.1653154492378235</v>
+        <v>-0.1374541074037552</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1742915660142899</v>
+        <v>0.145176574587822</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>-0.2762688100337982</v>
+        <v>-0.2365393489599228</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1108516007661819</v>
+        <v>0.09138184785842896</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0.1234699413180351</v>
+        <v>0.1604588478803635</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1783729195594788</v>
+        <v>0.1705322265625</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>-0.0671762153506279</v>
+        <v>-0.0485801137983799</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>0.01999727264046669</v>
+        <v>-0.001270380336791277</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>-0.3046898543834686</v>
+        <v>-0.2826021313667297</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.01543736644089222</v>
+        <v>-0.02480869553983212</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>-0.1913294792175293</v>
+        <v>-0.1494030356407166</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0.04240727424621582</v>
+        <v>0.03910664841532707</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>-0.8628815412521362</v>
+        <v>-0.8364272713661194</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0.118059866130352</v>
+        <v>0.08581703901290894</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0.3338916599750519</v>
+        <v>0.3516534268856049</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>0.03227648511528969</v>
+        <v>0.01346800290048122</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0.2067530006170273</v>
+        <v>0.2318429201841354</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.0276342649012804</v>
+        <v>-0.0322749949991703</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -7210,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0.246440663933754</v>
+        <v>0.3035806119441986</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.202647939324379</v>
+        <v>-0.2077621966600418</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0.1185359880328178</v>
+        <v>0.172122910618782</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.2458078414201736</v>
+        <v>-0.2431570738554001</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -7292,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0.6025597453117371</v>
+        <v>0.617857038974762</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.2394772469997406</v>
+        <v>-0.2331585288047791</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -7333,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>0.6002238988876343</v>
+        <v>0.6353254914283752</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0.2075329273939133</v>
+        <v>0.252625435590744</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>0.2011855244636536</v>
+        <v>0.2589451372623444</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2649706304073334</v>
+        <v>0.2586110532283783</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>-0.2733562290668488</v>
+        <v>-0.1927496939897537</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0.2069854140281677</v>
+        <v>0.230127140879631</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>-0.4405848979949951</v>
+        <v>-0.3823160231113434</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>0.2069854140281677</v>
+        <v>0.230127140879631</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.2813626527786255</v>
+        <v>-0.2383104115724564</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2837288677692413</v>
+        <v>0.2893141806125641</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>-0.1897139996290207</v>
+        <v>-0.1130650490522385</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -7555,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3481537997722626</v>
+        <v>0.3412388563156128</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>-0.2501445114612579</v>
+        <v>-0.1822514235973358</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3372970223426819</v>
+        <v>0.3452744483947754</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>-0.5134775042533875</v>
+        <v>-0.4471372663974762</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0.3463725447654724</v>
+        <v>0.3472679555416107</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>-0.4454126358032227</v>
+        <v>-0.3842379748821259</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>0.06634512543678284</v>
+        <v>0.04763837531208992</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -7702,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>0.08669080585241318</v>
+        <v>0.1234152019023895</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>0.05395585298538208</v>
+        <v>0.01923350803554058</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>-0.5711004137992859</v>
+        <v>-0.4864347279071808</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>0.176869124174118</v>
+        <v>0.1725539416074753</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.0452134944498539</v>
+        <v>-0.03415693342685699</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -7801,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1950192749500275</v>
+        <v>0.1656601130962372</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -7825,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>0.1843336820602417</v>
+        <v>0.2053069919347763</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>0.2302319407463074</v>
+        <v>0.1918536722660065</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0.278468906879425</v>
+        <v>0.2864815592765808</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.04330582171678543</v>
+        <v>-0.06551496684551239</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>-0.1069863140583038</v>
+        <v>-0.05446827784180641</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.0006370181799866259</v>
+        <v>-0.01893220841884613</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>0.0628570020198822</v>
+        <v>0.1010154858231544</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0.3866913020610809</v>
+        <v>0.3517867624759674</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0.8446719646453857</v>
+        <v>0.8217921257019043</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4764681756496429</v>
+        <v>0.3956698775291443</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>0.1854387074708939</v>
+        <v>0.1868160963058472</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4249800443649292</v>
+        <v>0.3620137274265289</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>-0.250369131565094</v>
+        <v>-0.1756599396467209</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>0.3866913020610809</v>
+        <v>0.3517867624759674</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>-0.1500845849514008</v>
+        <v>-0.1034255251288414</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3388267159461975</v>
+        <v>0.3072811961174011</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0.1167327091097832</v>
+        <v>0.1404299885034561</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0.3881294429302216</v>
+        <v>0.3414386212825775</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0.3208362758159637</v>
+        <v>0.3463689684867859</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.5339614152908325</v>
+        <v>0.4610742330551147</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8235,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>0.2946359515190125</v>
+        <v>0.3282552361488342</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -8252,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>0.06700500100851059</v>
+        <v>-0.01092764642089605</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>-0.2738269865512848</v>
+        <v>-0.251781553030014</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.1963432431221008</v>
+        <v>-0.2593308389186859</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -8317,10 +8317,10 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>-1.648417472839355</v>
+        <v>-1.52985668182373</v>
       </c>
       <c r="L192" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.1851044893264771</v>
+        <v>-0.1980993747711182</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -8358,10 +8358,10 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>-0.6270816326141357</v>
+        <v>-0.5469556450843811</v>
       </c>
       <c r="L193" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
@@ -8375,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.1853782534599304</v>
+        <v>-0.2165144979953766</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -8399,10 +8399,10 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>-0.4380317330360413</v>
+        <v>-0.342363029718399</v>
       </c>
       <c r="L194" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.2209460586309433</v>
+        <v>-0.257472813129425</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0.01216640882194042</v>
+        <v>0.08035784959793091</v>
       </c>
       <c r="L195" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -8457,7 +8457,7 @@
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.07481539994478226</v>
+        <v>-0.128643736243248</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -8481,10 +8481,10 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>-0.7784734964370728</v>
+        <v>-0.6837314963340759</v>
       </c>
       <c r="L196" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.01704290322959423</v>
+        <v>-0.07847440987825394</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -8522,10 +8522,10 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>-0.1222817972302437</v>
+        <v>-0.000958980992436409</v>
       </c>
       <c r="L197" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -8539,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1816741675138474</v>
+        <v>0.1374730467796326</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>1.021474838256836</v>
+        <v>1.051983594894409</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.6929294466972351</v>
+        <v>-0.6816230416297913</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -8604,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>-1.711094498634338</v>
+        <v>-1.591173648834229</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -8621,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.7109020352363586</v>
+        <v>-0.7019466161727905</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>0.249251052737236</v>
+        <v>0.2692456245422363</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.6788236498832703</v>
+        <v>-0.6860604882240295</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -8686,7 +8686,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>0.2099186331033707</v>
+        <v>0.2941198945045471</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.6348175406455994</v>
+        <v>-0.6298537254333496</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -8727,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>-0.2258329093456268</v>
+        <v>-0.1720818132162094</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -8744,7 +8744,7 @@
         <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.5861917734146118</v>
+        <v>-0.5718990564346313</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -8768,7 +8768,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>0.1427986919879913</v>
+        <v>0.1769961714744568</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.5326143503189087</v>
+        <v>-0.5551010370254517</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>-0.3203912377357483</v>
+        <v>-0.2510194778442383</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -8826,7 +8826,7 @@
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.5375881791114807</v>
+        <v>-0.5389938354492188</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -8850,7 +8850,7 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>-0.2701960206031799</v>
+        <v>-0.2518069744110107</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -8867,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.5404210090637207</v>
+        <v>-0.554524838924408</v>
       </c>
       <c r="D206" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.3417127132415771</v>
+        <v>-0.3017696142196655</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.6153411269187927</v>
+        <v>-0.5994142293930054</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>-0.2277200520038605</v>
+        <v>-0.1771407425403595</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.265229195356369</v>
+        <v>-0.3177414834499359</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -8973,10 +8973,10 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>2.391131401062012</v>
+        <v>2.259728193283081</v>
       </c>
       <c r="L208" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.2766848206520081</v>
+        <v>-0.3348844647407532</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -9014,10 +9014,10 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>-0.06604408472776413</v>
+        <v>0.01473685167729855</v>
       </c>
       <c r="L209" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.2617475986480713</v>
+        <v>-0.306239128112793</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -9055,10 +9055,10 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>-0.3605772852897644</v>
+        <v>-0.2877285480499268</v>
       </c>
       <c r="L210" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.2000158280134201</v>
+        <v>-0.2260473668575287</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -9096,10 +9096,10 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>-0.680908739566803</v>
+        <v>-0.5646271705627441</v>
       </c>
       <c r="L211" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.1827276349067688</v>
+        <v>-0.2136488556861877</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -9137,10 +9137,10 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>-0.1038343086838722</v>
+        <v>-0.04901548847556114</v>
       </c>
       <c r="L212" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
         <v>0</v>
@@ -9154,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.2404386252164841</v>
+        <v>-0.307924211025238</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -9178,10 +9178,10 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>-0.5422494411468506</v>
+        <v>-0.4599612057209015</v>
       </c>
       <c r="L213" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.18519327044487</v>
+        <v>-0.2341804802417755</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -9219,10 +9219,10 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>-0.4120883345603943</v>
+        <v>-0.3209081888198853</v>
       </c>
       <c r="L214" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
         <v>0</v>
@@ -9236,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.2016981244087219</v>
+        <v>-0.2279137074947357</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -9260,10 +9260,10 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>0.06137296557426453</v>
+        <v>0.1533755511045456</v>
       </c>
       <c r="L215" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.05894038081169128</v>
+        <v>-0.06977065652608871</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -9301,10 +9301,10 @@
         <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>-0.3992764055728912</v>
+        <v>-0.2670785486698151</v>
       </c>
       <c r="L216" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.0478440523147583</v>
+        <v>-0.106248065829277</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -9342,10 +9342,10 @@
         <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0.1506763249635696</v>
+        <v>0.2480642944574356</v>
       </c>
       <c r="L217" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1360930800437927</v>
+        <v>-0.1738165616989136</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -9383,10 +9383,10 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>0.1215817481279373</v>
+        <v>0.188513770699501</v>
       </c>
       <c r="L218" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -9400,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.1734800785779953</v>
+        <v>-0.2142102271318436</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -9424,10 +9424,10 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>0.07881513983011246</v>
+        <v>0.09855377674102783</v>
       </c>
       <c r="L219" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -9441,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.1863493323326111</v>
+        <v>-0.212713822722435</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -9465,10 +9465,10 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>-0.1184945479035378</v>
+        <v>-0.04245993122458458</v>
       </c>
       <c r="L220" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.1748294234275818</v>
+        <v>-0.2078408002853394</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -9506,10 +9506,10 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>-0.08444347977638245</v>
+        <v>-0.01327287405729294</v>
       </c>
       <c r="L221" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.1734800785779953</v>
+        <v>-0.2142102271318436</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -9547,10 +9547,10 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>-0.05816206336021423</v>
+        <v>0.01679302006959915</v>
       </c>
       <c r="L222" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.3684191405773163</v>
+        <v>-0.3825247883796692</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -9588,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>-1.703245282173157</v>
+        <v>-1.594676613807678</v>
       </c>
       <c r="L223" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.3829942941665649</v>
+        <v>-0.3907027542591095</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>-0.6585394144058228</v>
+        <v>-0.5649987459182739</v>
       </c>
       <c r="L224" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.3157462477684021</v>
+        <v>-0.3378476798534393</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -9670,10 +9670,10 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.7638731598854065</v>
+        <v>-0.6232516765594482</v>
       </c>
       <c r="L225" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.3388868868350983</v>
+        <v>-0.3429593145847321</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.409062922000885</v>
+        <v>-0.3276863992214203</v>
       </c>
       <c r="L226" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.2613004446029663</v>
+        <v>-0.2695762813091278</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -9752,10 +9752,10 @@
         <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.3720687627792358</v>
+        <v>-0.2555343508720398</v>
       </c>
       <c r="L227" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.2864623069763184</v>
+        <v>-0.2611074447631836</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -9793,10 +9793,10 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.1077727749943733</v>
+        <v>0.006125588435679674</v>
       </c>
       <c r="L228" t="n">
-        <v>0.02495281933256617</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.5559103488922119</v>
+        <v>-0.5317338109016418</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -9834,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.6768782138824463</v>
+        <v>-0.5418024063110352</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -9851,7 +9851,7 @@
         <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.4756955504417419</v>
+        <v>-0.4906011819839478</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -9875,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>0.4284857213497162</v>
+        <v>0.4740565419197083</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -9892,7 +9892,7 @@
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.4790379405021667</v>
+        <v>-0.4965747594833374</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.5745682716369629</v>
+        <v>-0.485819935798645</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.3469427824020386</v>
+        <v>-0.3659815490245819</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>0.2585231065750122</v>
+        <v>0.2721769511699677</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -9974,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.3612585067749023</v>
+        <v>-0.3882935345172882</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>-0.2660892307758331</v>
+        <v>-0.2078586518764496</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -10015,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.4198189675807953</v>
+        <v>-0.4649847149848938</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -10039,7 +10039,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>-0.2858957946300507</v>
+        <v>-0.2051275670528412</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -10056,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.4240483045578003</v>
+        <v>-0.4613029062747955</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -10080,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>-0.09111209958791733</v>
+        <v>-0.04694613814353943</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -10097,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.3892827928066254</v>
+        <v>-0.4587410688400269</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>2.64168381690979</v>
+        <v>2.590155124664307</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -10138,7 +10138,7 @@
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.09848874807357788</v>
+        <v>-0.1998570561408997</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -10162,7 +10162,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>0.3599988520145416</v>
+        <v>0.3275476098060608</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.03743996843695641</v>
+        <v>-0.1335144490003586</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -10203,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>-0.5662140846252441</v>
+        <v>-0.5576949715614319</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -10220,7 +10220,7 @@
         <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.09438843280076981</v>
+        <v>-0.1578550636768341</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -10244,7 +10244,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>-0.04136404395103455</v>
+        <v>-0.07835213840007782</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -10261,7 +10261,7 @@
         <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.1246892362833023</v>
+        <v>-0.1991439908742905</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>-0.1037950068712234</v>
+        <v>-0.1073008179664612</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.1587287485599518</v>
+        <v>-0.2589245736598969</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>0.05554156377911568</v>
+        <v>-0.01537829171866179</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.06344300508499146</v>
+        <v>-0.1518245935440063</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>-0.3518101871013641</v>
+        <v>-0.4013276696205139</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -10384,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.06344300508499146</v>
+        <v>-0.1518245935440063</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -10408,7 +10408,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>0.1184770315885544</v>
+        <v>0.06160377338528633</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -10425,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.05499359220266342</v>
+        <v>-0.1482421904802322</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -10449,7 +10449,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>-0.04496632888913155</v>
+        <v>-0.09898041933774948</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -10466,7 +10466,7 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.07839040458202362</v>
+        <v>-0.1474130600690842</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>-0.05284279957413673</v>
+        <v>-0.06844054162502289</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -10507,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.09152740985155106</v>
+        <v>-0.1734517067670822</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0.1743036508560181</v>
+        <v>0.1445057839155197</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.06321826577186584</v>
+        <v>-0.1525394916534424</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -10572,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0.01689215190708637</v>
+        <v>-0.0452532060444355</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.1006279215216637</v>
+        <v>-0.1780717819929123</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>0.1102879643440247</v>
+        <v>0.05002559348940849</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.1598852723836899</v>
+        <v>-0.252741277217865</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -10654,7 +10654,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>0.2449074983596802</v>
+        <v>0.2253398448228836</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -10671,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.1055920422077179</v>
+        <v>-0.1863857060670853</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>-0.7209352254867554</v>
+        <v>-0.7256937026977539</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -10712,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.02814478240907192</v>
+        <v>-0.1209503784775734</v>
       </c>
       <c r="D251" t="n">
         <v>0</v>
@@ -10736,7 +10736,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="n">
-        <v>-0.4258123934268951</v>
+        <v>-0.3956421613693237</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.04547597840428352</v>
+        <v>-0.1119585409760475</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -10777,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>-0.084991455078125</v>
+        <v>-0.1069466024637222</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.1160960122942924</v>
+        <v>-0.1759663671255112</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -10818,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>-0.8473134636878967</v>
+        <v>-0.8697508573532104</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.1203059181571007</v>
+        <v>-0.1750581711530685</v>
       </c>
       <c r="D254" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="n">
-        <v>-0.5089479684829712</v>
+        <v>-0.4769622385501862</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.1715536117553711</v>
+        <v>-0.2311428189277649</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -10900,7 +10900,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>-0.1604304015636444</v>
+        <v>-0.1321510225534439</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -10917,7 +10917,7 @@
         <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.1670017391443253</v>
+        <v>-0.2451926618814468</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -10941,7 +10941,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>-0.4450682103633881</v>
+        <v>-0.4528213739395142</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -10958,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.1383330672979355</v>
+        <v>-0.2262832075357437</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -10982,7 +10982,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>-0.4814485013484955</v>
+        <v>-0.4767837226390839</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.1074213907122612</v>
+        <v>-0.151195228099823</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="n">
-        <v>-0.3765892088413239</v>
+        <v>-0.4115222692489624</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.1411482989788055</v>
+        <v>-0.1891940087080002</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -11064,7 +11064,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.2516611516475677</v>
+        <v>-0.2810104489326477</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.1903308033943176</v>
+        <v>-0.2509329617023468</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
@@ -11105,7 +11105,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.2218902707099915</v>
+        <v>-0.2509820163249969</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -11122,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.1277592778205872</v>
+        <v>-0.1733092814683914</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.5823143124580383</v>
+        <v>-0.5859981179237366</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.1176335662603378</v>
+        <v>-0.1716024726629257</v>
       </c>
       <c r="D262" t="n">
         <v>0</v>
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>-0.3426990509033203</v>
+        <v>-0.3304227888584137</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -11204,7 +11204,7 @@
         <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.07000110298395157</v>
+        <v>-0.0882449671626091</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.4221532344818115</v>
+        <v>-0.4161835014820099</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -11245,7 +11245,7 @@
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.2677283585071564</v>
+        <v>-0.3560669422149658</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5414272546768188</v>
+        <v>0.5267632007598877</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -11286,7 +11286,7 @@
         <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.2603903710842133</v>
+        <v>-0.3640569448471069</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="K265" t="n">
-        <v>-0.1542903333902359</v>
+        <v>-0.1836299300193787</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -11327,7 +11327,7 @@
         <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2615973055362701</v>
+        <v>-0.3639838993549347</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -11351,7 +11351,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>-0.7298808097839355</v>
+        <v>-0.7465971112251282</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -11368,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.2461891025304794</v>
+        <v>-0.3529735803604126</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -11392,7 +11392,7 @@
         <v>0</v>
       </c>
       <c r="K267" t="n">
-        <v>-0.9390121698379517</v>
+        <v>-0.9110693335533142</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.1179937943816185</v>
+        <v>-0.1589981764554977</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -11433,7 +11433,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>-1.098724246025085</v>
+        <v>-1.062645554542542</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -11450,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.1203059181571007</v>
+        <v>-0.1750581711530685</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>-0.1482015997171402</v>
+        <v>-0.1882944107055664</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.1119758114218712</v>
+        <v>-0.1536789089441299</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -11515,7 +11515,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>-0.1106948330998421</v>
+        <v>-0.1038608402013779</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -11532,7 +11532,7 @@
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.1184303238987923</v>
+        <v>-0.1554352045059204</v>
       </c>
       <c r="D271" t="n">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>-0.3175917267799377</v>
+        <v>-0.2779667675495148</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -11573,7 +11573,7 @@
         <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.1182874366641045</v>
+        <v>-0.1656409054994583</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -11597,7 +11597,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>-0.2137428224086761</v>
+        <v>-0.1818287968635559</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -11614,7 +11614,7 @@
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.1109561622142792</v>
+        <v>-0.1617671698331833</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -11638,7 +11638,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>-0.1610514372587204</v>
+        <v>-0.1803814023733139</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -11655,7 +11655,7 @@
         <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.2647339403629303</v>
+        <v>-0.3499516248703003</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0.2368233948945999</v>
+        <v>0.2396985739469528</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -11696,7 +11696,7 @@
         <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.2505481541156769</v>
+        <v>-0.3691852390766144</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>-0.2184368968009949</v>
+        <v>-0.2565301954746246</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.2789476811885834</v>
+        <v>-0.3415942192077637</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -11761,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>-0.981429398059845</v>
+        <v>-0.9794725179672241</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -11778,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.1562519967556</v>
+        <v>-0.2390951216220856</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -11802,7 +11802,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>-0.8646048903465271</v>
+        <v>-0.8372077345848083</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -11819,7 +11819,7 @@
         <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.1430914103984833</v>
+        <v>-0.2387737482786179</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -11843,7 +11843,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>-0.1108428090810776</v>
+        <v>-0.1170616671442986</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -11860,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.2263481020927429</v>
+        <v>-0.2717415988445282</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>-0.05552717298269272</v>
+        <v>-0.04315148666501045</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -11901,7 +11901,7 @@
         <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.2475733757019043</v>
+        <v>-0.3164175450801849</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -11925,7 +11925,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>-0.3487637341022491</v>
+        <v>-0.3322595357894897</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -11942,7 +11942,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.2607970833778381</v>
+        <v>-0.3565594255924225</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -11966,7 +11966,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>-0.1972162425518036</v>
+        <v>-0.1979294717311859</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -11983,7 +11983,7 @@
         <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.2543194591999054</v>
+        <v>-0.3671748340129852</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -12007,7 +12007,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>-0.5785030126571655</v>
+        <v>-0.5890598297119141</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -12024,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.2802887260913849</v>
+        <v>-0.3613131642341614</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -12048,7 +12048,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>-0.172905221581459</v>
+        <v>-0.1597785651683807</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -12065,7 +12065,7 @@
         <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.3961539566516876</v>
+        <v>-0.5150083899497986</v>
       </c>
       <c r="D284" t="n">
         <v>0</v>
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>-0.4511486291885376</v>
+        <v>-0.4261654019355774</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -12106,7 +12106,7 @@
         <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.3994103372097015</v>
+        <v>-0.5020230412483215</v>
       </c>
       <c r="D285" t="n">
         <v>0</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K285" t="n">
-        <v>-1.868582248687744</v>
+        <v>-1.829020619392395</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -12147,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.3805882930755615</v>
+        <v>-0.4815325736999512</v>
       </c>
       <c r="D286" t="n">
         <v>0</v>
@@ -12171,7 +12171,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>-1.059321522712708</v>
+        <v>-1.030590772628784</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -12188,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.4088565111160278</v>
+        <v>-0.4834703505039215</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -12212,7 +12212,7 @@
         <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>-1.335371136665344</v>
+        <v>-1.269204378128052</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.3828627169132233</v>
+        <v>-0.5220633745193481</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>-0.1437142342329025</v>
+        <v>-0.1617262959480286</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -12270,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.3925613760948181</v>
+        <v>-0.5090750455856323</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -12294,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>-1.195924401283264</v>
+        <v>-1.151329755783081</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.3997252583503723</v>
+        <v>-0.5000693202018738</v>
       </c>
       <c r="D290" t="n">
         <v>0</v>
@@ -12335,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>-1.181884288787842</v>
+        <v>-1.134654641151428</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -12352,7 +12352,7 @@
         <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.3712644279003143</v>
+        <v>-0.4879054725170135</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>-0.8735342621803284</v>
+        <v>-0.8326195478439331</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -12393,7 +12393,7 @@
         <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.3762609362602234</v>
+        <v>-0.4799772202968597</v>
       </c>
       <c r="D292" t="n">
         <v>0</v>
@@ -12417,7 +12417,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>-1.272030115127563</v>
+        <v>-1.211589097976685</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -12434,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.3797802031040192</v>
+        <v>-0.4788385033607483</v>
       </c>
       <c r="D293" t="n">
         <v>0</v>
@@ -12458,7 +12458,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>-0.9656935930252075</v>
+        <v>-0.9336463212966919</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -12475,7 +12475,7 @@
         <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>0.5369613766670227</v>
+        <v>0.3367357850074768</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>0.2353010922670364</v>
+        <v>0.2781558632850647</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -12516,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0.5426302552223206</v>
+        <v>0.3324202001094818</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -12540,7 +12540,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>0.2703209519386292</v>
+        <v>0.2748067378997803</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>0.5246909856796265</v>
+        <v>0.3475446999073029</v>
       </c>
       <c r="D296" t="n">
         <v>0</v>
@@ -12581,7 +12581,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>0.1428121030330658</v>
+        <v>0.1441830098628998</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -12598,7 +12598,7 @@
         <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.3795832097530365</v>
+        <v>-0.4803207814693451</v>
       </c>
       <c r="D297" t="n">
         <v>0</v>
@@ -12622,7 +12622,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>-1.377340793609619</v>
+        <v>-1.368858695030212</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -12639,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.3916467130184174</v>
+        <v>-0.4779760539531708</v>
       </c>
       <c r="D298" t="n">
         <v>0</v>
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>-1.848700881004333</v>
+        <v>-1.76874828338623</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -12680,7 +12680,7 @@
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.389595627784729</v>
+        <v>-0.4800264537334442</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -12704,7 +12704,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
-        <v>-0.7923991680145264</v>
+        <v>-0.7500555515289307</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -12721,7 +12721,7 @@
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.3764722645282745</v>
+        <v>-0.4793383777141571</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>-0.7204349040985107</v>
+        <v>-0.7257505655288696</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -12762,7 +12762,7 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.3972991406917572</v>
+        <v>-0.4724445641040802</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -12786,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="K301" t="n">
-        <v>-1.320220351219177</v>
+        <v>-1.277158975601196</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -12800,40 +12800,40 @@
         <v>145.975</v>
       </c>
       <c r="B302" t="n">
-        <v>201.33740234375</v>
+        <v>201.1555633544922</v>
       </c>
       <c r="C302" t="n">
-        <v>205.1895294189453</v>
+        <v>204.8129730224609</v>
       </c>
       <c r="D302" t="n">
-        <v>200.5308514967704</v>
+        <v>199.8925571234974</v>
       </c>
       <c r="E302" t="n">
-        <v>208.7191395759583</v>
+        <v>206.7561420426908</v>
       </c>
       <c r="F302" t="n">
-        <v>201.5786956921602</v>
+        <v>201.3787998776778</v>
       </c>
       <c r="G302" t="n">
-        <v>204.0780944824219</v>
+        <v>203.1624908447266</v>
       </c>
       <c r="H302" t="n">
-        <v>200.2404532594985</v>
+        <v>200.3844387339313</v>
       </c>
       <c r="I302" t="n">
-        <v>154.5645960011411</v>
+        <v>171.9614519419278</v>
       </c>
       <c r="J302" t="n">
-        <v>181.1547241210938</v>
+        <v>180.3915100097656</v>
       </c>
       <c r="K302" t="n">
-        <v>150.3453826904297</v>
+        <v>152.0090637207031</v>
       </c>
       <c r="L302" t="n">
-        <v>177.9620664991237</v>
+        <v>176.8880894702059</v>
       </c>
       <c r="M302" t="n">
-        <v>177.9620664991237</v>
+        <v>176.8880894702059</v>
       </c>
     </row>
     <row r="303">
@@ -12841,40 +12841,40 @@
         <v>210.69</v>
       </c>
       <c r="B303" t="n">
-        <v>201.32177734375</v>
+        <v>201.2347869873047</v>
       </c>
       <c r="C303" t="n">
-        <v>205.3167114257812</v>
+        <v>204.9430236816406</v>
       </c>
       <c r="D303" t="n">
-        <v>200.3340438617191</v>
+        <v>199.6976409358338</v>
       </c>
       <c r="E303" t="n">
-        <v>208.0977864265442</v>
+        <v>206.1205670689654</v>
       </c>
       <c r="F303" t="n">
-        <v>201.5786956921602</v>
+        <v>201.3787998776778</v>
       </c>
       <c r="G303" t="n">
-        <v>203.6353759765625</v>
+        <v>202.6217193603516</v>
       </c>
       <c r="H303" t="n">
-        <v>199.82921492802</v>
+        <v>199.3661580592444</v>
       </c>
       <c r="I303" t="n">
-        <v>205.7734254113135</v>
+        <v>202.0486645174487</v>
       </c>
       <c r="J303" t="n">
-        <v>199.0716247558594</v>
+        <v>198.7266845703125</v>
       </c>
       <c r="K303" t="n">
-        <v>204.3213806152344</v>
+        <v>203.9076995849609</v>
       </c>
       <c r="L303" t="n">
-        <v>200.0954625122006</v>
+        <v>200.5981606699892</v>
       </c>
       <c r="M303" t="n">
-        <v>200.0954625122006</v>
+        <v>200.5981606699892</v>
       </c>
     </row>
     <row r="304">
@@ -12882,40 +12882,40 @@
         <v>202.07</v>
       </c>
       <c r="B304" t="n">
-        <v>201.3029632568359</v>
+        <v>201.1838531494141</v>
       </c>
       <c r="C304" t="n">
-        <v>205.1701812744141</v>
+        <v>204.7999267578125</v>
       </c>
       <c r="D304" t="n">
-        <v>201.4574211529523</v>
+        <v>200.9544976289054</v>
       </c>
       <c r="E304" t="n">
-        <v>211.2870411872864</v>
+        <v>209.7450139140536</v>
       </c>
       <c r="F304" t="n">
-        <v>201.5786956921602</v>
+        <v>201.7505597998046</v>
       </c>
       <c r="G304" t="n">
-        <v>205.7765502929688</v>
+        <v>205.1060638427734</v>
       </c>
       <c r="H304" t="n">
-        <v>202.184363897632</v>
+        <v>202.6162130931383</v>
       </c>
       <c r="I304" t="n">
-        <v>201.9138638614787</v>
+        <v>202.5405255794964</v>
       </c>
       <c r="J304" t="n">
-        <v>199.6920471191406</v>
+        <v>199.269287109375</v>
       </c>
       <c r="K304" t="n">
-        <v>205.5748443603516</v>
+        <v>205.0577697753906</v>
       </c>
       <c r="L304" t="n">
-        <v>202.0602240719636</v>
+        <v>202.2979957176018</v>
       </c>
       <c r="M304" t="n">
-        <v>202.0602240719636</v>
+        <v>202.2979957176018</v>
       </c>
     </row>
     <row r="305">
@@ -12923,40 +12923,40 @@
         <v>206.935</v>
       </c>
       <c r="B305" t="n">
-        <v>201.1902313232422</v>
+        <v>201.0621643066406</v>
       </c>
       <c r="C305" t="n">
-        <v>204.8764495849609</v>
+        <v>204.5623016357422</v>
       </c>
       <c r="D305" t="n">
-        <v>204.4730603646985</v>
+        <v>204.0632634153794</v>
       </c>
       <c r="E305" t="n">
-        <v>219.1983094215393</v>
+        <v>217.9639965678451</v>
       </c>
       <c r="F305" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G305" t="n">
-        <v>210.9822998046875</v>
+        <v>210.4384155273438</v>
       </c>
       <c r="H305" t="n">
-        <v>202.6788506547815</v>
+        <v>203.0241936401073</v>
       </c>
       <c r="I305" t="n">
-        <v>203.4029512471921</v>
+        <v>203.829412020145</v>
       </c>
       <c r="J305" t="n">
-        <v>199.9091033935547</v>
+        <v>199.5420074462891</v>
       </c>
       <c r="K305" t="n">
-        <v>205.3402099609375</v>
+        <v>204.8282623291016</v>
       </c>
       <c r="L305" t="n">
-        <v>202.6573272624403</v>
+        <v>203.0907184542637</v>
       </c>
       <c r="M305" t="n">
-        <v>202.6573272624403</v>
+        <v>203.0907184542637</v>
       </c>
     </row>
     <row r="306">
@@ -12964,40 +12964,40 @@
         <v>195.745</v>
       </c>
       <c r="B306" t="n">
-        <v>201.1334381103516</v>
+        <v>200.9809417724609</v>
       </c>
       <c r="C306" t="n">
-        <v>204.7982940673828</v>
+        <v>204.4210052490234</v>
       </c>
       <c r="D306" t="n">
-        <v>204.7186787470711</v>
+        <v>204.2646015500723</v>
       </c>
       <c r="E306" t="n">
-        <v>219.5932259559631</v>
+        <v>218.2424405654454</v>
       </c>
       <c r="F306" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G306" t="n">
-        <v>211.5186920166016</v>
+        <v>210.8158111572266</v>
       </c>
       <c r="H306" t="n">
-        <v>202.6788506547815</v>
+        <v>202.6553725904766</v>
       </c>
       <c r="I306" t="n">
-        <v>203.2518845467522</v>
+        <v>202.8658520571296</v>
       </c>
       <c r="J306" t="n">
-        <v>200.2593231201172</v>
+        <v>199.8783111572266</v>
       </c>
       <c r="K306" t="n">
-        <v>204.7895660400391</v>
+        <v>204.3259735107422</v>
       </c>
       <c r="L306" t="n">
-        <v>202.6573272624403</v>
+        <v>203.0907184542637</v>
       </c>
       <c r="M306" t="n">
-        <v>202.6573272624403</v>
+        <v>203.0907184542637</v>
       </c>
     </row>
     <row r="307">
@@ -13005,40 +13005,40 @@
         <v>202.99</v>
       </c>
       <c r="B307" t="n">
-        <v>200.9243469238281</v>
+        <v>200.81640625</v>
       </c>
       <c r="C307" t="n">
-        <v>204.5531616210938</v>
+        <v>204.1986236572266</v>
       </c>
       <c r="D307" t="n">
-        <v>205.3896505558034</v>
+        <v>204.9797504317769</v>
       </c>
       <c r="E307" t="n">
-        <v>220.8782410621643</v>
+        <v>219.6836195913855</v>
       </c>
       <c r="F307" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G307" t="n">
-        <v>212.68115234375</v>
+        <v>212.1287231445312</v>
       </c>
       <c r="H307" t="n">
-        <v>200.8886205820975</v>
+        <v>200.7104260995818</v>
       </c>
       <c r="I307" t="n">
-        <v>203.0458765651419</v>
+        <v>199.7629678033688</v>
       </c>
       <c r="J307" t="n">
-        <v>200.1184692382812</v>
+        <v>199.8037719726562</v>
       </c>
       <c r="K307" t="n">
-        <v>204.5782623291016</v>
+        <v>204.1113586425781</v>
       </c>
       <c r="L307" t="n">
-        <v>201.3958909975335</v>
+        <v>202.3661395222146</v>
       </c>
       <c r="M307" t="n">
-        <v>201.3958909975335</v>
+        <v>202.3661395222146</v>
       </c>
     </row>
     <row r="308">
@@ -13046,40 +13046,40 @@
         <v>176.54</v>
       </c>
       <c r="B308" t="n">
-        <v>200.8419799804688</v>
+        <v>200.6253967285156</v>
       </c>
       <c r="C308" t="n">
-        <v>204.38623046875</v>
+        <v>204.0158081054688</v>
       </c>
       <c r="D308" t="n">
-        <v>205.6643553255622</v>
+        <v>204.9043697650019</v>
       </c>
       <c r="E308" t="n">
-        <v>221.2800812721252</v>
+        <v>219.104100419914</v>
       </c>
       <c r="F308" t="n">
-        <v>201.6275113118743</v>
+        <v>201.2950486111071</v>
       </c>
       <c r="G308" t="n">
-        <v>213.1935424804688</v>
+        <v>212.0931854248047</v>
       </c>
       <c r="H308" t="n">
-        <v>200.8886205820975</v>
+        <v>200.6781598918939</v>
       </c>
       <c r="I308" t="n">
-        <v>203.0458765651419</v>
+        <v>197.6822733070316</v>
       </c>
       <c r="J308" t="n">
-        <v>200.2445983886719</v>
+        <v>199.8578796386719</v>
       </c>
       <c r="K308" t="n">
-        <v>204.3802947998047</v>
+        <v>203.8950347900391</v>
       </c>
       <c r="L308" t="n">
-        <v>201.3958909975335</v>
+        <v>201.9009125876908</v>
       </c>
       <c r="M308" t="n">
-        <v>201.3958909975335</v>
+        <v>201.9009125876908</v>
       </c>
     </row>
     <row r="309">
@@ -13087,40 +13087,40 @@
         <v>192.15</v>
       </c>
       <c r="B309" t="n">
-        <v>200.8268585205078</v>
+        <v>200.6334228515625</v>
       </c>
       <c r="C309" t="n">
-        <v>204.4033203125</v>
+        <v>204.0309753417969</v>
       </c>
       <c r="D309" t="n">
-        <v>205.6578916839208</v>
+        <v>204.8979061233605</v>
       </c>
       <c r="E309" t="n">
-        <v>221.2707657814026</v>
+        <v>219.0940711229849</v>
       </c>
       <c r="F309" t="n">
-        <v>201.6275113118743</v>
+        <v>201.2950486111071</v>
       </c>
       <c r="G309" t="n">
-        <v>213.1745300292969</v>
+        <v>212.0518493652344</v>
       </c>
       <c r="H309" t="n">
-        <v>200.8886205820975</v>
+        <v>200.6781598918939</v>
       </c>
       <c r="I309" t="n">
-        <v>205.1071143387015</v>
+        <v>197.6822733070316</v>
       </c>
       <c r="J309" t="n">
-        <v>200.0416259765625</v>
+        <v>199.6405639648438</v>
       </c>
       <c r="K309" t="n">
-        <v>203.6913909912109</v>
+        <v>203.2203216552734</v>
       </c>
       <c r="L309" t="n">
-        <v>200.9061786401339</v>
+        <v>201.9009125876908</v>
       </c>
       <c r="M309" t="n">
-        <v>200.9061786401339</v>
+        <v>201.9009125876908</v>
       </c>
     </row>
     <row r="310">
@@ -13128,40 +13128,40 @@
         <v>199.325</v>
       </c>
       <c r="B310" t="n">
-        <v>200.9288330078125</v>
+        <v>200.9019317626953</v>
       </c>
       <c r="C310" t="n">
-        <v>204.6231231689453</v>
+        <v>204.2969207763672</v>
       </c>
       <c r="D310" t="n">
-        <v>205.1496337727387</v>
+        <v>204.8773474820311</v>
       </c>
       <c r="E310" t="n">
-        <v>220.3690781593323</v>
+        <v>219.5698828801931</v>
       </c>
       <c r="F310" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G310" t="n">
-        <v>212.3011932373047</v>
+        <v>211.935302734375</v>
       </c>
       <c r="H310" t="n">
-        <v>200.9551362603929</v>
+        <v>200.7104260995818</v>
       </c>
       <c r="I310" t="n">
-        <v>206.0602626049414</v>
+        <v>204.4353194388003</v>
       </c>
       <c r="J310" t="n">
-        <v>200.2233734130859</v>
+        <v>199.9525604248047</v>
       </c>
       <c r="K310" t="n">
-        <v>203.8712005615234</v>
+        <v>203.4286193847656</v>
       </c>
       <c r="L310" t="n">
-        <v>200.9061786401339</v>
+        <v>201.9009125876908</v>
       </c>
       <c r="M310" t="n">
-        <v>200.9061786401339</v>
+        <v>201.9009125876908</v>
       </c>
     </row>
     <row r="311">
@@ -13169,40 +13169,40 @@
         <v>214.17</v>
       </c>
       <c r="B311" t="n">
-        <v>201.060302734375</v>
+        <v>200.9493560791016</v>
       </c>
       <c r="C311" t="n">
-        <v>204.7581329345703</v>
+        <v>204.3613739013672</v>
       </c>
       <c r="D311" t="n">
-        <v>204.8962862199252</v>
+        <v>204.4472050055562</v>
       </c>
       <c r="E311" t="n">
-        <v>220.0178742408752</v>
+        <v>218.6843776636859</v>
       </c>
       <c r="F311" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G311" t="n">
-        <v>211.9208831787109</v>
+        <v>211.2016296386719</v>
       </c>
       <c r="H311" t="n">
-        <v>202.753075894253</v>
+        <v>202.6553725904766</v>
       </c>
       <c r="I311" t="n">
-        <v>203.2518845467522</v>
+        <v>204.4353194388003</v>
       </c>
       <c r="J311" t="n">
-        <v>200.2701873779297</v>
+        <v>199.9754486083984</v>
       </c>
       <c r="K311" t="n">
-        <v>204.2490692138672</v>
+        <v>203.7012329101562</v>
       </c>
       <c r="L311" t="n">
-        <v>202.6573272624403</v>
+        <v>202.4004491493434</v>
       </c>
       <c r="M311" t="n">
-        <v>202.6573272624403</v>
+        <v>202.4004491493434</v>
       </c>
     </row>
     <row r="312">
@@ -13210,40 +13210,40 @@
         <v>222.47</v>
       </c>
       <c r="B312" t="n">
-        <v>200.943115234375</v>
+        <v>200.8604888916016</v>
       </c>
       <c r="C312" t="n">
-        <v>204.6242218017578</v>
+        <v>204.2591094970703</v>
       </c>
       <c r="D312" t="n">
-        <v>205.1754883393043</v>
+        <v>204.9032020485967</v>
       </c>
       <c r="E312" t="n">
-        <v>220.4083542823792</v>
+        <v>219.6101789839893</v>
       </c>
       <c r="F312" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G312" t="n">
-        <v>212.2964172363281</v>
+        <v>211.990478515625</v>
       </c>
       <c r="H312" t="n">
-        <v>200.603897065353</v>
+        <v>200.7104260995818</v>
       </c>
       <c r="I312" t="n">
-        <v>203.2518845467522</v>
+        <v>204.5645844106823</v>
       </c>
       <c r="J312" t="n">
-        <v>200.2121887207031</v>
+        <v>199.9369506835938</v>
       </c>
       <c r="K312" t="n">
-        <v>204.7228546142578</v>
+        <v>204.1496124267578</v>
       </c>
       <c r="L312" t="n">
-        <v>201.3958909975335</v>
+        <v>202.3661395222146</v>
       </c>
       <c r="M312" t="n">
-        <v>201.3958909975335</v>
+        <v>202.3661395222146</v>
       </c>
     </row>
     <row r="313">
@@ -13251,40 +13251,40 @@
         <v>220.715</v>
       </c>
       <c r="B313" t="n">
-        <v>200.9364013671875</v>
+        <v>200.8193054199219</v>
       </c>
       <c r="C313" t="n">
-        <v>204.5715026855469</v>
+        <v>204.1840667724609</v>
       </c>
       <c r="D313" t="n">
-        <v>205.3961141974448</v>
+        <v>204.9862140734183</v>
       </c>
       <c r="E313" t="n">
-        <v>220.8878312110901</v>
+        <v>219.693595835154</v>
       </c>
       <c r="F313" t="n">
-        <v>201.6275113118743</v>
+        <v>202.8658073816733</v>
       </c>
       <c r="G313" t="n">
-        <v>212.72509765625</v>
+        <v>212.1458282470703</v>
       </c>
       <c r="H313" t="n">
-        <v>200.8886205820975</v>
+        <v>200.7104260995818</v>
       </c>
       <c r="I313" t="n">
-        <v>203.0458765651419</v>
+        <v>199.6337028314868</v>
       </c>
       <c r="J313" t="n">
-        <v>200.3092346191406</v>
+        <v>200.0358123779297</v>
       </c>
       <c r="K313" t="n">
-        <v>204.4926300048828</v>
+        <v>204.0146179199219</v>
       </c>
       <c r="L313" t="n">
-        <v>201.3958909975335</v>
+        <v>201.9009125876908</v>
       </c>
       <c r="M313" t="n">
-        <v>201.3958909975335</v>
+        <v>201.9009125876908</v>
       </c>
     </row>
     <row r="314">
@@ -13292,40 +13292,40 @@
         <v>192.635</v>
       </c>
       <c r="B314" t="n">
-        <v>200.5491027832031</v>
+        <v>200.3555145263672</v>
       </c>
       <c r="C314" t="n">
-        <v>204.0941619873047</v>
+        <v>203.7379455566406</v>
       </c>
       <c r="D314" t="n">
-        <v>206.4979232220653</v>
+        <v>205.4858381295435</v>
       </c>
       <c r="E314" t="n">
-        <v>222.6005845069885</v>
+        <v>219.8085608879308</v>
       </c>
       <c r="F314" t="n">
-        <v>201.6275113118743</v>
+        <v>198.1489997904914</v>
       </c>
       <c r="G314" t="n">
-        <v>214.6177520751953</v>
+        <v>213.219970703125</v>
       </c>
       <c r="H314" t="n">
-        <v>200.1580982500896</v>
+        <v>200.1534336918053</v>
       </c>
       <c r="I314" t="n">
-        <v>201.1174852146653</v>
+        <v>197.6822733070316</v>
       </c>
       <c r="J314" t="n">
-        <v>200.1399230957031</v>
+        <v>199.7206115722656</v>
       </c>
       <c r="K314" t="n">
-        <v>204.5083770751953</v>
+        <v>204.0413665771484</v>
       </c>
       <c r="L314" t="n">
-        <v>201.3958909975335</v>
+        <v>201.5857773558591</v>
       </c>
       <c r="M314" t="n">
-        <v>201.3958909975335</v>
+        <v>201.5857773558591</v>
       </c>
     </row>
     <row r="315">
@@ -13333,40 +13333,40 @@
         <v>193.565</v>
       </c>
       <c r="B315" t="n">
-        <v>199.2438201904297</v>
+        <v>199.0238647460938</v>
       </c>
       <c r="C315" t="n">
-        <v>202.0545959472656</v>
+        <v>201.5613403320312</v>
       </c>
       <c r="D315" t="n">
-        <v>206.5991901269599</v>
+        <v>205.4160152706841</v>
       </c>
       <c r="E315" t="n">
-        <v>222.6548390388489</v>
+        <v>219.5519295702914</v>
       </c>
       <c r="F315" t="n">
-        <v>194.2528865990446</v>
+        <v>195.4010676128642</v>
       </c>
       <c r="G315" t="n">
-        <v>212.2780914306641</v>
+        <v>210.6286468505859</v>
       </c>
       <c r="H315" t="n">
-        <v>199.8236032399075</v>
+        <v>198.4476625010757</v>
       </c>
       <c r="I315" t="n">
-        <v>195.8045509776653</v>
+        <v>188.6242834595656</v>
       </c>
       <c r="J315" t="n">
-        <v>199.541259765625</v>
+        <v>199.0689239501953</v>
       </c>
       <c r="K315" t="n">
-        <v>203.4275054931641</v>
+        <v>202.9847412109375</v>
       </c>
       <c r="L315" t="n">
-        <v>200.3906725573539</v>
+        <v>199.9315787249635</v>
       </c>
       <c r="M315" t="n">
-        <v>200.3906725573539</v>
+        <v>199.9315787249635</v>
       </c>
     </row>
   </sheetData>

--- a/data/reports/TEC22_Data/B2_final_predictions_comparison.xlsx
+++ b/data/reports/TEC22_Data/B2_final_predictions_comparison.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Actual_N</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LSTM_custom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>LSTM_mae</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Polynomial (d=2)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Boosting</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MLP</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RandomForest</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Boosting_custom_with_window</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>LSTM_custom_with_window</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>LSTM_mae_with_window</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>RandomForest_mae_with_window</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>RandomForest_custom_with_window</t>
         </is>
@@ -503,7 +491,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.507258296012878</v>
+        <v>-3.555799007415771</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.025321245193481</v>
+        <v>-2.44350266456604</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -544,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.519555568695068</v>
+        <v>-3.528115272521973</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -568,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8044549226760864</v>
+        <v>-2.581721305847168</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -585,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.610749244689941</v>
+        <v>-3.65718674659729</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -609,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.991117537021637</v>
+        <v>-2.624469041824341</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -626,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.403019070625305</v>
+        <v>-3.528138399124146</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -650,10 +638,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5783096551895142</v>
+        <v>-2.461087226867676</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.2396171568627451</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -667,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.283248662948608</v>
+        <v>-3.389600992202759</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -691,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.105843067169189</v>
+        <v>-2.316039800643921</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.2396171568627451</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -708,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.197530508041382</v>
+        <v>-3.188476085662842</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -732,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.806309700012207</v>
+        <v>-2.3020920753479</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2396171568627451</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -749,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.184786558151245</v>
+        <v>-3.274708986282349</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -773,10 +761,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.595441222190857</v>
+        <v>-2.253519773483276</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2396171568627451</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -790,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4520705938339233</v>
+        <v>-0.35454922914505</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -814,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.14750862121582</v>
+        <v>-0.4108503460884094</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -831,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.4442669749259949</v>
+        <v>-0.3685167729854584</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -855,7 +843,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.039299726486206</v>
+        <v>-1.158908843994141</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -872,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4274004995822906</v>
+        <v>-0.3190543949604034</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -896,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.676832914352417</v>
+        <v>-1.081480979919434</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -913,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.4510971903800964</v>
+        <v>-0.3789576590061188</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -937,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.045265436172485</v>
+        <v>-1.203146696090698</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -954,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5330066084861755</v>
+        <v>-0.4311593174934387</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -978,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.288878440856934</v>
+        <v>-1.374664425849915</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -995,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.5110474824905396</v>
+        <v>-0.4501658976078033</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1019,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1.827998042106628</v>
+        <v>-1.311263084411621</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1036,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.5151006579399109</v>
+        <v>-0.4081306457519531</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1060,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.885879635810852</v>
+        <v>-1.245646834373474</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1077,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0007957308553159237</v>
+        <v>1.067327976226807</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1101,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.57631254196167</v>
+        <v>-0.2754518687725067</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1118,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.01504645869135857</v>
+        <v>1.060924768447876</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1142,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.505748510360718</v>
+        <v>-0.2799167931079865</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1159,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.04065250232815742</v>
+        <v>1.078523874282837</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1183,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.788768649101257</v>
+        <v>-0.2930831611156464</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1200,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.01237665303051472</v>
+        <v>1.101454854011536</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1224,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.458411931991577</v>
+        <v>-0.2437561452388763</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1241,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.03131569549441338</v>
+        <v>1.103963494300842</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1265,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.600017309188843</v>
+        <v>-0.2640833854675293</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1282,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02521103248000145</v>
+        <v>0.9244569540023804</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1306,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9177400469779968</v>
+        <v>-0.2050616592168808</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1323,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0787583664059639</v>
+        <v>0.8897203207015991</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1347,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8739262819290161</v>
+        <v>-0.1889528930187225</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1364,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09445604681968689</v>
+        <v>0.8944177627563477</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1388,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.479663133621216</v>
+        <v>-0.2798606157302856</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1405,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1464801579713821</v>
+        <v>0.9801937937736511</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1429,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8633168935775757</v>
+        <v>-0.1445171684026718</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1446,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5718590617179871</v>
+        <v>0.4746873676776886</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1470,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7519617080688477</v>
+        <v>-1.384122371673584</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.2396171568627451</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1487,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02199834212660789</v>
+        <v>0.01917528547346592</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1511,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.418078660964966</v>
+        <v>-0.9457761645317078</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1528,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0239874292165041</v>
+        <v>0.05918586999177933</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1552,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.514674961566925</v>
+        <v>-0.2177939414978027</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1569,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1217682063579559</v>
+        <v>0.1982022523880005</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1593,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8775262832641602</v>
+        <v>-0.6511800289154053</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1610,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1225728243589401</v>
+        <v>0.1646151691675186</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1634,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.3626236915588379</v>
+        <v>-0.3935219347476959</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1651,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1080762892961502</v>
+        <v>0.2086703777313232</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1675,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2745660543441772</v>
+        <v>-0.1355531811714172</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1692,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.08449450135231018</v>
+        <v>0.1803625673055649</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1716,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2901721894741058</v>
+        <v>-0.2168290913105011</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1733,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04879119619727135</v>
+        <v>0.1064430177211761</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1757,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3463284969329834</v>
+        <v>-0.2209795713424683</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1774,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02006818354129791</v>
+        <v>0.08109833300113678</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1798,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5106121301651001</v>
+        <v>-0.09563245624303818</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1815,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.007997265085577965</v>
+        <v>0.04413038119673729</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1839,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3771247863769531</v>
+        <v>-0.06082544103264809</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1856,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.02492060139775276</v>
+        <v>0.009069495834410191</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1880,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.402353048324585</v>
+        <v>0.03382273018360138</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1897,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0668613463640213</v>
+        <v>0.1321018934249878</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1921,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.4513961970806122</v>
+        <v>-0.07805906236171722</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -1938,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1021045446395874</v>
+        <v>0.1643548905849457</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1962,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.05142535269260406</v>
+        <v>-0.1611275523900986</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1979,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.02639969438314438</v>
+        <v>0.06725578010082245</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2003,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.4767184853553772</v>
+        <v>-0.1972174495458603</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2020,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3678495287895203</v>
+        <v>0.1382290720939636</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2044,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9035325646400452</v>
+        <v>0.02009936794638634</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2061,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5036921501159668</v>
+        <v>0.3398591279983521</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2085,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.259088546037674</v>
+        <v>0.2531049847602844</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2102,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4650399684906006</v>
+        <v>0.3808510005474091</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2126,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.31769660115242</v>
+        <v>0.1644582450389862</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2143,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4278698563575745</v>
+        <v>0.2852536141872406</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2167,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.4679215550422668</v>
+        <v>0.08152294158935547</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2184,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3604919016361237</v>
+        <v>0.1393718421459198</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2208,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4886069595813751</v>
+        <v>0.02116282656788826</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2225,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4173192083835602</v>
+        <v>0.1779900938272476</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2249,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.4886018931865692</v>
+        <v>0.06488075852394104</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2266,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3604239225387573</v>
+        <v>0.1017257422208786</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2290,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5044524073600769</v>
+        <v>0.1034534052014351</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2307,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3690476715564728</v>
+        <v>0.1495402604341507</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2331,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1353858560323715</v>
+        <v>0.238318145275116</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2348,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4161312282085419</v>
+        <v>0.2538703083992004</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2372,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.03708448261022568</v>
+        <v>0.2328252345323563</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2389,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3947464227676392</v>
+        <v>0.1998968571424484</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2413,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2917254567146301</v>
+        <v>0.1001861467957497</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2430,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3787252902984619</v>
+        <v>0.1652214676141739</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2454,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5106433033943176</v>
+        <v>0.1721527576446533</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2471,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4428098797798157</v>
+        <v>0.3779160678386688</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2495,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.08263418823480606</v>
+        <v>0.2951164543628693</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2512,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4895933270454407</v>
+        <v>0.3885089159011841</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2536,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.364960789680481</v>
+        <v>-0.02453011274337769</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2553,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4676096737384796</v>
+        <v>0.3050796389579773</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2577,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.2584083080291748</v>
+        <v>-0.1570592671632767</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2594,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5222913026809692</v>
+        <v>0.3347700834274292</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2618,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.9957094192504883</v>
+        <v>-0.1413991451263428</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2635,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3671641945838928</v>
+        <v>0.007077604066580534</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2659,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3927279114723206</v>
+        <v>-0.02904302626848221</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2676,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4855882525444031</v>
+        <v>0.36031574010849</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2700,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4079687297344208</v>
+        <v>-0.09461581707000732</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2717,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3716127276420593</v>
+        <v>0.03143094107508659</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2741,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3508070707321167</v>
+        <v>0.009418756701052189</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2758,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3518302142620087</v>
+        <v>0.06074927002191544</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2782,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6005841493606567</v>
+        <v>-0.08638604730367661</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2799,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3556859195232391</v>
+        <v>0.05844356492161751</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2823,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3960760831832886</v>
+        <v>-0.1318672001361847</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2840,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4908654391765594</v>
+        <v>0.366491824388504</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2864,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.07033757865428925</v>
+        <v>-0.1190692633390427</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2881,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3808857202529907</v>
+        <v>0.09080447256565094</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2905,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01420252025127411</v>
+        <v>-0.09996479004621506</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -2922,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2274413704872131</v>
+        <v>0.5059629678726196</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2946,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4857290685176849</v>
+        <v>-0.1560389250516891</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -2963,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4770731925964355</v>
+        <v>0.5390453934669495</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2987,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8311400413513184</v>
+        <v>-0.1358034759759903</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3004,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4458993077278137</v>
+        <v>0.5169435739517212</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3028,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1877285689115524</v>
+        <v>-0.128900408744812</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3045,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5888864398002625</v>
+        <v>0.6010056138038635</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3069,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2175334244966507</v>
+        <v>-0.2369318157434464</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3086,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2826806902885437</v>
+        <v>0.5020517110824585</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3110,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.1228745654225349</v>
+        <v>0.03361186385154724</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3127,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1780244112014771</v>
+        <v>0.5631503462791443</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3151,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.353028804063797</v>
+        <v>0.08799340575933456</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3168,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.01516741141676903</v>
+        <v>0.4774850308895111</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3192,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2638311088085175</v>
+        <v>0.08966310322284698</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3209,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2274413704872131</v>
+        <v>0.5059629678726196</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3233,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7460066080093384</v>
+        <v>-0.1228780224919319</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3250,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3417956233024597</v>
+        <v>0.5062589049339294</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3274,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4809013307094574</v>
+        <v>-0.1211332976818085</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3291,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3815886080265045</v>
+        <v>0.1558572351932526</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3315,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1.079559564590454</v>
+        <v>0.1188607960939407</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3332,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2037657201290131</v>
+        <v>0.1177607625722885</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3356,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.1657246351242065</v>
+        <v>0.03153534978628159</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3373,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2205461710691452</v>
+        <v>0.1100565493106842</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3397,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2364084273576736</v>
+        <v>-0.00933566503226757</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3414,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2189720720052719</v>
+        <v>0.1080569103360176</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3438,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1859750598669052</v>
+        <v>0.01011285558342934</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3455,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.124521017074585</v>
+        <v>0.1330954730510712</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3479,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.01844462566077709</v>
+        <v>0.0766662135720253</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3496,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1753922998905182</v>
+        <v>0.141156017780304</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3520,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2421718537807465</v>
+        <v>0.008659109473228455</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3537,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1243032142519951</v>
+        <v>0.1338804364204407</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -3561,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.03492189571261406</v>
+        <v>0.04113908857107162</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3578,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1666427701711655</v>
+        <v>0.1411795765161514</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -3602,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3172064125537872</v>
+        <v>0.02086329273879528</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -3619,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4527062177658081</v>
+        <v>0.2140444070100784</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3643,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.02248783223330975</v>
+        <v>-0.225037693977356</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -3660,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2899472415447235</v>
+        <v>0.1517039835453033</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3684,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.1142466589808464</v>
+        <v>0.03848882019519806</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -3701,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.260907918214798</v>
+        <v>0.1067060828208923</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3725,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.08663016557693481</v>
+        <v>-0.01089206896722317</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -3742,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1703907251358032</v>
+        <v>0.1333046555519104</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3766,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.1641914695501328</v>
+        <v>0.01664413325488567</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3783,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1476080119609833</v>
+        <v>0.154179647564888</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3807,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2827472686767578</v>
+        <v>0.1025440469384193</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3824,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.149766594171524</v>
+        <v>0.1581059396266937</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3848,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.2954680919647217</v>
+        <v>0.09544491022825241</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3865,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.05263902992010117</v>
+        <v>0.09435606002807617</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3889,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.08177661895751953</v>
+        <v>0.009338526055216789</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -3906,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.0009101519244723022</v>
+        <v>0.0872412770986557</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3930,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.3417676687240601</v>
+        <v>-0.03660747781395912</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -3947,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.148757129907608</v>
+        <v>0.1583077013492584</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3971,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.1585191488265991</v>
+        <v>-0.1743488311767578</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -3988,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.148757129907608</v>
+        <v>0.1583077013492584</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4012,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.09875886142253876</v>
+        <v>0.01620887778699398</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4029,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3022564947605133</v>
+        <v>0.1454218327999115</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -4053,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.08917650580406189</v>
+        <v>-0.1544276028871536</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4070,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2970139980316162</v>
+        <v>0.1485877633094788</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -4094,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1285916864871979</v>
+        <v>-0.0009816831443458796</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4111,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2659927308559418</v>
+        <v>0.1413777619600296</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -4135,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1324300467967987</v>
+        <v>0.003640766721218824</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4152,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2920457124710083</v>
+        <v>0.154700756072998</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -4176,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.2593081295490265</v>
+        <v>0.01845047809183598</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4193,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3517081439495087</v>
+        <v>0.3401476442813873</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4217,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.8780971169471741</v>
+        <v>-0.7528610825538635</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4234,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3591855466365814</v>
+        <v>0.3354965448379517</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4258,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.286223292350769</v>
+        <v>-0.187656357884407</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4275,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4390591382980347</v>
+        <v>0.3391174972057343</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4299,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4294322431087494</v>
+        <v>-0.2595877051353455</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4316,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4002144634723663</v>
+        <v>0.3444280326366425</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4340,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1946838945150375</v>
+        <v>-0.1642334312200546</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4357,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2812260389328003</v>
+        <v>0.3430257737636566</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4381,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.03503068163990974</v>
+        <v>-0.0629228800535202</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4398,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2489759922027588</v>
+        <v>0.3389117121696472</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4422,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.2227085381746292</v>
+        <v>-0.1375771015882492</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4439,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3907236754894257</v>
+        <v>0.3455980718135834</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4463,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.5598306655883789</v>
+        <v>-0.3055716156959534</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4480,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4390591382980347</v>
+        <v>0.3391174972057343</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4504,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.3247912228107452</v>
+        <v>-0.2160347551107407</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4521,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3105390965938568</v>
+        <v>0.1713653206825256</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4545,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.3392259478569031</v>
+        <v>0.3788726627826691</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4562,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2443978786468506</v>
+        <v>0.1810662895441055</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4586,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.1564558148384094</v>
+        <v>0.02089543081820011</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -4603,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0.07576925307512283</v>
+        <v>0.1499730348587036</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4627,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>-0.332452654838562</v>
+        <v>0.1009835973381996</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -4644,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3359309136867523</v>
+        <v>0.1701876074075699</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -4668,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0.5902566909790039</v>
+        <v>-0.2431144118309021</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -4685,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3808048069477081</v>
+        <v>0.176777645945549</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4709,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0.06491103023290634</v>
+        <v>-0.06682955473661423</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -4726,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3931067883968353</v>
+        <v>0.1700604110956192</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -4750,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0.01430009119212627</v>
+        <v>-0.04468405991792679</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -4767,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2033475786447525</v>
+        <v>0.1645724773406982</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -4791,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>-0.4522269368171692</v>
+        <v>0.1320564150810242</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -4808,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2383726239204407</v>
+        <v>0.1703847199678421</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -4832,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1150195971131325</v>
+        <v>-0.06706296652555466</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -4849,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.04720554500818253</v>
+        <v>0.074066162109375</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4873,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0.2490997761487961</v>
+        <v>0.4321930706501007</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -4890,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2127164006233215</v>
+        <v>0.06452305614948273</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -4914,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>-1.188729643821716</v>
+        <v>-0.4004594385623932</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -4931,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.03755772858858109</v>
+        <v>0.02703797072172165</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4955,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>-0.43694207072258</v>
+        <v>0.1658284068107605</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -4972,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.4388670027256012</v>
+        <v>-0.1304083317518234</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4996,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>-0.7369498014450073</v>
+        <v>0.1315289735794067</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5013,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.5673802495002747</v>
+        <v>-0.224538579583168</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5037,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0.1881997883319855</v>
+        <v>-0.02856829017400742</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5054,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.4994640052318573</v>
+        <v>-0.1226723194122314</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5078,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2657261192798615</v>
+        <v>-0.02472184598445892</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5095,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.3705262541770935</v>
+        <v>-0.02618996985256672</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -5119,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>0.190461739897728</v>
+        <v>0.01663835346698761</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5136,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.3525842130184174</v>
+        <v>-0.0279035996645689</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -5160,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>0.001117072300985456</v>
+        <v>-0.009780863299965858</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5177,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.308197021484375</v>
+        <v>-0.01053350232541561</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -5201,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2072803378105164</v>
+        <v>0.002220951020717621</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5218,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.2535033524036407</v>
+        <v>0.06095016375184059</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -5242,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1387604027986526</v>
+        <v>0.07079053670167923</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5259,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.272540420293808</v>
+        <v>0.0009307442232966423</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -5283,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0.1437118053436279</v>
+        <v>0.08247958123683929</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5300,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.3105489313602448</v>
+        <v>-0.0007068153354339302</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -5324,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>-0.2671183049678802</v>
+        <v>-0.02507918514311314</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5341,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3338532447814941</v>
+        <v>-0.0147211579605937</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -5365,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0.1797103732824326</v>
+        <v>0.0733899399638176</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5382,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.3063251376152039</v>
+        <v>-8.595309191150591e-05</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -5406,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0.14820796251297</v>
+        <v>0.03235701844096184</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -5423,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.4019091427326202</v>
+        <v>-0.0268473643809557</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -5447,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>0.05886899679899216</v>
+        <v>0.08568724244832993</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -5464,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.5250374674797058</v>
+        <v>-0.1590376347303391</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -5488,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>0.2333372384309769</v>
+        <v>0.01366629637777805</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -5505,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.5936648845672607</v>
+        <v>-0.1251868009567261</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -5529,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0.1827743947505951</v>
+        <v>0.08647076040506363</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -5546,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.5346775650978088</v>
+        <v>-0.1583905965089798</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -5570,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>0.3509689271450043</v>
+        <v>-0.06510552018880844</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -5587,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.5362618565559387</v>
+        <v>-0.136562779545784</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -5611,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>0.05849142745137215</v>
+        <v>-0.03190433233976364</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -5628,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.5270078182220459</v>
+        <v>-0.1561729311943054</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -5652,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>0.03064285591244698</v>
+        <v>-0.08335196971893311</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -5669,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.6099690198898315</v>
+        <v>-0.124530628323555</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -5693,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0.128355398774147</v>
+        <v>0.05892143771052361</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -5710,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.6560477614402771</v>
+        <v>-0.1352201998233795</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -5734,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>-0.3250101208686829</v>
+        <v>-0.07961466163396835</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -5751,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.3743190765380859</v>
+        <v>-0.03904634341597557</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -5775,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0.5269747376441956</v>
+        <v>-0.08459525555372238</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -5792,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.50612473487854</v>
+        <v>-0.08542046695947647</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -5816,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.7516465783119202</v>
+        <v>0.2471057176589966</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -5833,7 +5821,7 @@
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.2574857473373413</v>
+        <v>0.008891665376722813</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -5857,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1869187504053116</v>
+        <v>-0.3587490022182465</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -5874,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.413614958524704</v>
+        <v>-0.06933628767728806</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -5898,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.1088173389434814</v>
+        <v>-0.1190681084990501</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -5915,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.5104493498802185</v>
+        <v>-0.1802981197834015</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -5939,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>0.1903579235076904</v>
+        <v>-0.2154188603162766</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -5956,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.3735162913799286</v>
+        <v>-0.04093280434608459</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -5980,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0.5881383419036865</v>
+        <v>-0.2091670036315918</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -5997,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2651175856590271</v>
+        <v>-0.01032899506390095</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -6021,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0.304771363735199</v>
+        <v>-0.2336409240961075</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6038,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.1619544476270676</v>
+        <v>0.03239604830741882</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -6062,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0.3094973564147949</v>
+        <v>-0.1534721255302429</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6079,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.1170114502310753</v>
+        <v>-0.01337452046573162</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -6103,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0.1734148114919662</v>
+        <v>-0.1388509571552277</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6120,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.1464123725891113</v>
+        <v>0.03046618029475212</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -6144,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>-0.01663400419056416</v>
+        <v>-0.069839708507061</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6161,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.1716847866773605</v>
+        <v>0.03015826269984245</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -6185,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>-0.2034711688756943</v>
+        <v>-0.1611512005329132</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6202,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.1464123725891113</v>
+        <v>0.03046618029475212</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -6226,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>-0.001718050334602594</v>
+        <v>-0.1502739936113358</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6243,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.1528262048959732</v>
+        <v>-0.005301288329064846</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -6267,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>-0.3605692684650421</v>
+        <v>-0.2459719628095627</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6284,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.1363417059183121</v>
+        <v>-0.03614902496337891</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -6308,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>-0.09663234651088715</v>
+        <v>-0.19902703166008</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -6325,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.17634417116642</v>
+        <v>0.03572220727801323</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6349,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>-0.4009875655174255</v>
+        <v>-0.1586751490831375</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -6366,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.2536799907684326</v>
+        <v>-0.01283810846507549</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -6390,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>-0.1636396795511246</v>
+        <v>-0.153052881360054</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -6407,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.1464123725891113</v>
+        <v>-0.02931641973555088</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -6431,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0.361905962228775</v>
+        <v>-0.1904505044221878</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -6448,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0.03322646394371986</v>
+        <v>0.06405022740364075</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -6472,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0.5016351938247681</v>
+        <v>-0.05874840170145035</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -6489,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.004306657239794731</v>
+        <v>0.04355038702487946</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -6513,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0.1312482059001923</v>
+        <v>0.009774187579751015</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -6530,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.01406103279441595</v>
+        <v>0.05247372761368752</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -6554,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0.1359298974275589</v>
+        <v>0.01195919886231422</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -6571,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0.153400331735611</v>
+        <v>0.09887365996837616</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -6595,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0.3842870593070984</v>
+        <v>-0.04710722342133522</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -6612,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2018401920795441</v>
+        <v>0.1200653985142708</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6636,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0.1137275323271751</v>
+        <v>0.0180251058191061</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -6653,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1342938840389252</v>
+        <v>0.102191373705864</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -6677,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>0.03763875365257263</v>
+        <v>0.1377255618572235</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -6694,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1519325971603394</v>
+        <v>0.09499230235815048</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -6718,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0.1112513616681099</v>
+        <v>0.0541737861931324</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -6735,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1796956211328506</v>
+        <v>0.1136681661009789</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -6759,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0.2558496594429016</v>
+        <v>0.09147673100233078</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -6776,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>0.2809526324272156</v>
+        <v>0.1508369892835617</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -6800,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1840247958898544</v>
+        <v>0.1079503670334816</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -6817,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0.257355123758316</v>
+        <v>0.130214512348175</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -6841,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>-0.1374541074037552</v>
+        <v>0.08874507993459702</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -6858,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0.145176574587822</v>
+        <v>0.09270624816417694</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -6882,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>-0.2365393489599228</v>
+        <v>0.08594290167093277</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -6899,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>0.09138184785842896</v>
+        <v>0.09473975747823715</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -6923,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0.1604588478803635</v>
+        <v>0.1078507676720619</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -6940,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1705322265625</v>
+        <v>0.1141688525676727</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -6964,7 +6952,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>-0.0485801137983799</v>
+        <v>-0.04998384788632393</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -6981,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.001270380336791277</v>
+        <v>0.04036659374833107</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -7005,7 +6993,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>-0.2826021313667297</v>
+        <v>0.03843408077955246</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7022,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.02480869553983212</v>
+        <v>0.04838404804468155</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -7046,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>-0.1494030356407166</v>
+        <v>-0.07931703329086304</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7063,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0.03910664841532707</v>
+        <v>0.246193990111351</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -7087,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>-0.8364272713661194</v>
+        <v>0.2976879775524139</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7104,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08581703901290894</v>
+        <v>0.2595238387584686</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -7128,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0.3516534268856049</v>
+        <v>-0.1349669992923737</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7145,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>0.01346800290048122</v>
+        <v>0.2103162258863449</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -7169,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0.2318429201841354</v>
+        <v>-0.117605984210968</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7186,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.0322749949991703</v>
+        <v>0.2307028919458389</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -7210,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0.3035806119441986</v>
+        <v>-0.1386829316616058</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7227,7 +7215,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.2077621966600418</v>
+        <v>0.1772575229406357</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -7251,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0.172122910618782</v>
+        <v>-0.1992355287075043</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -7268,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.2431570738554001</v>
+        <v>0.1154267936944962</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -7292,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0.617857038974762</v>
+        <v>-0.2481353580951691</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -7309,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.2331585288047791</v>
+        <v>0.1424349099397659</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -7333,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>0.6353254914283752</v>
+        <v>-0.3417569994926453</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -7350,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0.252625435590744</v>
+        <v>0.1983824223279953</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -7374,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>0.2589451372623444</v>
+        <v>-0.2726050615310669</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -7391,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2586110532283783</v>
+        <v>0.1969692260026932</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -7415,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>-0.1927496939897537</v>
+        <v>0.1115920692682266</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -7432,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0.230127140879631</v>
+        <v>0.2018827944993973</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -7456,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>-0.3823160231113434</v>
+        <v>0.1492482572793961</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -7473,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>0.230127140879631</v>
+        <v>0.2018827944993973</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -7497,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.2383104115724564</v>
+        <v>0.09300712496042252</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -7514,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2893141806125641</v>
+        <v>0.1929257959127426</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -7538,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>-0.1130650490522385</v>
+        <v>0.0561952143907547</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -7555,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>0.3412388563156128</v>
+        <v>0.2086044549942017</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -7579,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>-0.1822514235973358</v>
+        <v>0.1354257017374039</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -7596,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3452744483947754</v>
+        <v>0.1848715990781784</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -7620,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>-0.4471372663974762</v>
+        <v>0.1681944131851196</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -7637,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0.3472679555416107</v>
+        <v>0.2054369300603867</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -7661,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>-0.3842379748821259</v>
+        <v>0.1778674572706223</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -7678,7 +7666,7 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>0.04763837531208992</v>
+        <v>0.2557097673416138</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -7702,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>0.1234152019023895</v>
+        <v>0.2200136035680771</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -7719,7 +7707,7 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>0.01923350803554058</v>
+        <v>0.2351627498865128</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -7743,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>-0.4864347279071808</v>
+        <v>-0.3458910286426544</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -7760,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1725539416074753</v>
+        <v>0.2837408781051636</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -7784,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.03415693342685699</v>
+        <v>-0.2641039788722992</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -7801,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1656601130962372</v>
+        <v>0.3039906620979309</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -7825,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>0.2053069919347763</v>
+        <v>-0.05918741598725319</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -7842,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>0.1918536722660065</v>
+        <v>0.348332554101944</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -7866,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0.2864815592765808</v>
+        <v>0.002573780715465546</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -7883,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.06551496684551239</v>
+        <v>0.241091251373291</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -7907,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>-0.05446827784180641</v>
+        <v>-0.005902165081351995</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -7924,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.01893220841884613</v>
+        <v>0.2814248204231262</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -7948,7 +7936,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>0.1010154858231544</v>
+        <v>-0.2737126350402832</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -7965,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0.3517867624759674</v>
+        <v>0.2914720773696899</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -7989,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0.8217921257019043</v>
+        <v>-0.1850160956382751</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8006,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0.3956698775291443</v>
+        <v>0.2958167791366577</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -8030,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>0.1868160963058472</v>
+        <v>0.1388230174779892</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8047,7 +8035,7 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0.3620137274265289</v>
+        <v>0.2777442038059235</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -8071,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>-0.1756599396467209</v>
+        <v>0.2266955673694611</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -8088,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>0.3517867624759674</v>
+        <v>0.2914720773696899</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -8112,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>-0.1034255251288414</v>
+        <v>0.1817457526922226</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -8129,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3072811961174011</v>
+        <v>0.3058917224407196</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -8153,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0.1404299885034561</v>
+        <v>0.1440453976392746</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -8170,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0.3414386212825775</v>
+        <v>0.2974588572978973</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -8194,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0.3463689684867859</v>
+        <v>0.09232360869646072</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -8211,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4610742330551147</v>
+        <v>0.3173716366291046</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8235,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>0.3282552361488342</v>
+        <v>0.2101052403450012</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -8252,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.01092764642089605</v>
+        <v>-0.1564163565635681</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -8276,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>-0.251781553030014</v>
+        <v>0.2676055729389191</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -8293,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.2593308389186859</v>
+        <v>-0.2435314655303955</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -8317,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>-1.52985668182373</v>
+        <v>0.131899431347847</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -8334,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.1980993747711182</v>
+        <v>-0.2017710953950882</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -8358,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>-0.5469556450843811</v>
+        <v>-0.1769717037677765</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -8375,7 +8363,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.2165144979953766</v>
+        <v>-0.2007824331521988</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -8399,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>-0.342363029718399</v>
+        <v>-0.1372263580560684</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -8416,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.257472813129425</v>
+        <v>-0.2256405055522919</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -8440,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0.08035784959793091</v>
+        <v>0.0064673344604671</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -8457,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.128643736243248</v>
+        <v>-0.1008958071470261</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -8481,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>-0.6837314963340759</v>
+        <v>-0.1508320271968842</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -8498,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.07847440987825394</v>
+        <v>-0.0668688490986824</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -8522,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>-0.000958980992436409</v>
+        <v>-0.2786828279495239</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -8539,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1374730467796326</v>
+        <v>0.143863633275032</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
@@ -8563,10 +8551,10 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>1.051983594894409</v>
+        <v>0.2122888565063477</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>0.2396171568627451</v>
       </c>
       <c r="M198" t="n">
         <v>0</v>
@@ -8580,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.6816230416297913</v>
+        <v>-0.4607057869434357</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -8604,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>-1.591173648834229</v>
+        <v>0.03408515453338623</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -8621,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.7019466161727905</v>
+        <v>-0.4502309560775757</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -8645,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>0.2692456245422363</v>
+        <v>-0.3302456438541412</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -8662,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.6860604882240295</v>
+        <v>-0.418866366147995</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -8686,7 +8674,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>0.2941198945045471</v>
+        <v>-0.3468852937221527</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -8703,7 +8691,7 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.6298537254333496</v>
+        <v>-0.35755655169487</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -8727,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>-0.1720818132162094</v>
+        <v>-0.3522718250751495</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -8744,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.5718990564346313</v>
+        <v>-0.3132292628288269</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -8768,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>0.1769961714744568</v>
+        <v>-0.1632194370031357</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -8785,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.5551010370254517</v>
+        <v>-0.254585325717926</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -8809,10 +8797,10 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>-0.2510194778442383</v>
+        <v>-0.1321625709533691</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
@@ -8826,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.5389938354492188</v>
+        <v>-0.24884894490242</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -8850,10 +8838,10 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>-0.2518069744110107</v>
+        <v>-0.0541183240711689</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M205" t="n">
         <v>0</v>
@@ -8867,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.554524838924408</v>
+        <v>-0.2421666830778122</v>
       </c>
       <c r="D206" t="n">
         <v>0</v>
@@ -8891,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.3017696142196655</v>
+        <v>-0.0462002344429493</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M206" t="n">
         <v>0</v>
@@ -8908,7 +8896,7 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.5994142293930054</v>
+        <v>-0.395234614610672</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -8932,7 +8920,7 @@
         <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>-0.1771407425403595</v>
+        <v>-0.1763317137956619</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -8949,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.3177414834499359</v>
+        <v>-0.2508162558078766</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -8973,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>2.259728193283081</v>
+        <v>-0.1216454282402992</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -8990,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.3348844647407532</v>
+        <v>-0.273250550031662</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -9014,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>0.01473685167729855</v>
+        <v>0.1952397525310516</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -9031,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.306239128112793</v>
+        <v>-0.2763180434703827</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -9055,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>-0.2877285480499268</v>
+        <v>0.2299511581659317</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -9072,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.2260473668575287</v>
+        <v>-0.2149989753961563</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -9096,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>-0.5646271705627441</v>
+        <v>0.08511620759963989</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -9113,7 +9101,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.2136488556861877</v>
+        <v>-0.2191473841667175</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -9137,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>-0.04901548847556114</v>
+        <v>-0.01672947965562344</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -9154,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.307924211025238</v>
+        <v>-0.247689351439476</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -9178,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>-0.4599612057209015</v>
+        <v>-0.1304733455181122</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -9195,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.2341804802417755</v>
+        <v>-0.2160394191741943</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -9219,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>-0.3209081888198853</v>
+        <v>0.06429925560951233</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -9236,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.2279137074947357</v>
+        <v>-0.2261709123849869</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -9260,7 +9248,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>0.1533755511045456</v>
+        <v>-0.0200700331479311</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -9277,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.06977065652608871</v>
+        <v>-0.08370201289653778</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -9301,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>-0.2670785486698151</v>
+        <v>-0.129993811249733</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -9318,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.106248065829277</v>
+        <v>-0.04076610133051872</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -9342,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0.2480642944574356</v>
+        <v>-0.2649129629135132</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -9359,7 +9347,7 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.1738165616989136</v>
+        <v>-0.1583520174026489</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -9383,7 +9371,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>0.188513770699501</v>
+        <v>-0.2404821962118149</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -9400,7 +9388,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.2142102271318436</v>
+        <v>-0.2004400044679642</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -9424,7 +9412,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>0.09855377674102783</v>
+        <v>-0.1435407549142838</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -9441,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.212713822722435</v>
+        <v>-0.196235179901123</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -9465,7 +9453,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>-0.04245993122458458</v>
+        <v>-0.07333158701658249</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -9482,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.2078408002853394</v>
+        <v>-0.1707928329706192</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -9506,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>-0.01327287405729294</v>
+        <v>-0.07062871754169464</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -9523,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.2142102271318436</v>
+        <v>-0.2004400044679642</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -9547,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>0.01679302006959915</v>
+        <v>-0.08230932056903839</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -9564,7 +9552,7 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.3825247883796692</v>
+        <v>-0.2190651893615723</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -9588,7 +9576,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>-1.594676613807678</v>
+        <v>-0.3800496459007263</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -9605,7 +9593,7 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.3907027542591095</v>
+        <v>-0.2238879203796387</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -9629,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>-0.5649987459182739</v>
+        <v>-0.4076968431472778</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -9646,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.3378476798534393</v>
+        <v>-0.2159295976161957</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -9670,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.6232516765594482</v>
+        <v>-0.4635236859321594</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -9687,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.3429593145847321</v>
+        <v>-0.1960741430521011</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -9711,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.3276863992214203</v>
+        <v>-0.4760856926441193</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -9728,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.2695762813091278</v>
+        <v>-0.04601635038852692</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -9752,7 +9740,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.2555343508720398</v>
+        <v>-0.4522942006587982</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -9769,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.2611074447631836</v>
+        <v>-0.03656625002622604</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -9793,7 +9781,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>0.006125588435679674</v>
+        <v>-0.5590226054191589</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -9810,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.5317338109016418</v>
+        <v>-0.2611874043941498</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -9834,7 +9822,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.5418024063110352</v>
+        <v>0.1758556216955185</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -9851,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.4906011819839478</v>
+        <v>-0.1667663902044296</v>
       </c>
       <c r="D230" t="n">
         <v>0</v>
@@ -9875,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>0.4740565419197083</v>
+        <v>-0.2510090470314026</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -9892,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.4965747594833374</v>
+        <v>-0.2121306657791138</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -9916,7 +9904,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.485819935798645</v>
+        <v>-0.3907064497470856</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -9933,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.3659815490245819</v>
+        <v>-0.05440720915794373</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -9957,10 +9945,10 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>0.2721769511699677</v>
+        <v>-0.08462768048048019</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -9974,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.3882935345172882</v>
+        <v>-0.05166087299585342</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -9998,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>-0.2078586518764496</v>
+        <v>-0.05584779009222984</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -10015,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.4649847149848938</v>
+        <v>-0.1083386391401291</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -10039,10 +10027,10 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>-0.2051275670528412</v>
+        <v>-0.09812191128730774</v>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M234" t="n">
         <v>0</v>
@@ -10056,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.4613029062747955</v>
+        <v>-0.1104047521948814</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -10080,10 +10068,10 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>-0.04694613814353943</v>
+        <v>-0.1201499477028847</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>0.007998455665452021</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -10097,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.4587410688400269</v>
+        <v>-0.1585853099822998</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -10121,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>2.590155124664307</v>
+        <v>-0.3011917769908905</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -10138,7 +10126,7 @@
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.1998570561408997</v>
+        <v>-0.04677518829703331</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -10162,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>0.3275476098060608</v>
+        <v>0.6199181079864502</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -10179,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.1335144490003586</v>
+        <v>-0.01377937290817499</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -10203,7 +10191,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>-0.5576949715614319</v>
+        <v>0.2568129301071167</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -10220,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.1578550636768341</v>
+        <v>-0.0524442195892334</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -10244,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>-0.07835213840007782</v>
+        <v>0.2531976997852325</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -10261,7 +10249,7 @@
         <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.1991439908742905</v>
+        <v>-0.04832164943218231</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -10285,7 +10273,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>-0.1073008179664612</v>
+        <v>0.3585564196109772</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -10302,7 +10290,7 @@
         <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.2589245736598969</v>
+        <v>-0.04020049795508385</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -10326,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>-0.01537829171866179</v>
+        <v>0.4469192028045654</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -10343,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.1518245935440063</v>
+        <v>-0.04501375555992126</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -10367,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>-0.4013276696205139</v>
+        <v>0.4002499580383301</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -10384,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.1518245935440063</v>
+        <v>-0.04501375555992126</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -10408,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>0.06160377338528633</v>
+        <v>0.3462161719799042</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -10425,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.1482421904802322</v>
+        <v>-0.06670578569173813</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -10449,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>-0.09898041933774948</v>
+        <v>0.3067542612552643</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -10466,7 +10454,7 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.1474130600690842</v>
+        <v>-0.02792683616280556</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -10490,7 +10478,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>-0.06844054162502289</v>
+        <v>0.3194117546081543</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -10507,7 +10495,7 @@
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.1734517067670822</v>
+        <v>-0.05320375040173531</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -10531,7 +10519,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0.1445057839155197</v>
+        <v>0.326947420835495</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -10548,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.1525394916534424</v>
+        <v>-0.07498253881931305</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -10572,7 +10560,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>-0.0452532060444355</v>
+        <v>0.3503950834274292</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -10589,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.1780717819929123</v>
+        <v>-0.05836423113942146</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -10613,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>0.05002559348940849</v>
+        <v>0.3671177327632904</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -10630,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.252741277217865</v>
+        <v>-0.03344534710049629</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -10654,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>0.2253398448228836</v>
+        <v>0.4685356914997101</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -10671,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.1863857060670853</v>
+        <v>-0.06142779067158699</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -10695,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>-0.7256937026977539</v>
+        <v>0.3659223616123199</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -10712,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.1209503784775734</v>
+        <v>0.00230894167907536</v>
       </c>
       <c r="D251" t="n">
         <v>0</v>
@@ -10736,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="K251" t="n">
-        <v>-0.3956421613693237</v>
+        <v>0.2913019061088562</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -10753,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.1119585409760475</v>
+        <v>0.01825818233191967</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -10777,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>-0.1069466024637222</v>
+        <v>0.2601062953472137</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -10794,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.1759663671255112</v>
+        <v>-0.2484209090471268</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -10818,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>-0.8697508573532104</v>
+        <v>-0.3558893799781799</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -10835,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.1750581711530685</v>
+        <v>-0.2242408096790314</v>
       </c>
       <c r="D254" t="n">
         <v>0</v>
@@ -10859,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="n">
-        <v>-0.4769622385501862</v>
+        <v>5.975387102807872e-05</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -10876,7 +10864,7 @@
         <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.2311428189277649</v>
+        <v>-0.2592364847660065</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -10900,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>-0.1321510225534439</v>
+        <v>-0.01911096461117268</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -10917,7 +10905,7 @@
         <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.2451926618814468</v>
+        <v>-0.2621850669384003</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -10941,7 +10929,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>-0.4528213739395142</v>
+        <v>0.02736590057611465</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -10958,7 +10946,7 @@
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.2262832075357437</v>
+        <v>-0.2598452270030975</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -10982,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>-0.4767837226390839</v>
+        <v>0.07761291414499283</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -10999,7 +10987,7 @@
         <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.151195228099823</v>
+        <v>-0.2345647215843201</v>
       </c>
       <c r="D258" t="n">
         <v>0</v>
@@ -11023,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="n">
-        <v>-0.4115222692489624</v>
+        <v>0.04370565712451935</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -11040,7 +11028,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.1891940087080002</v>
+        <v>-0.2610051929950714</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -11064,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.2810104489326477</v>
+        <v>-0.001020469004288316</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -11081,7 +11069,7 @@
         <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.2509329617023468</v>
+        <v>-0.2764975726604462</v>
       </c>
       <c r="D260" t="n">
         <v>0</v>
@@ -11105,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.2509820163249969</v>
+        <v>0.02141958847641945</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -11122,7 +11110,7 @@
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.1733092814683914</v>
+        <v>-0.2485205680131912</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -11146,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.5859981179237366</v>
+        <v>0.1068843603134155</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -11163,7 +11151,7 @@
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.1716024726629257</v>
+        <v>-0.2405865788459778</v>
       </c>
       <c r="D262" t="n">
         <v>0</v>
@@ -11187,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>-0.3304227888584137</v>
+        <v>0.03037165850400925</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -11204,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.0882449671626091</v>
+        <v>-0.182089626789093</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -11228,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.4161835014820099</v>
+        <v>0.02652891352772713</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -11245,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.3560669422149658</v>
+        <v>-0.2689045667648315</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -11269,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5267632007598877</v>
+        <v>0.06796535849571228</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -11286,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.3640569448471069</v>
+        <v>-0.1319397836923599</v>
       </c>
       <c r="D265" t="n">
         <v>0</v>
@@ -11310,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="K265" t="n">
-        <v>-0.1836299300193787</v>
+        <v>0.3759763836860657</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -11327,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.3639838993549347</v>
+        <v>-0.1541745215654373</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -11351,7 +11339,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>-0.7465971112251282</v>
+        <v>0.4976882934570312</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -11368,7 +11356,7 @@
         <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.3529735803604126</v>
+        <v>-0.25824174284935</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -11392,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="K267" t="n">
-        <v>-0.9110693335533142</v>
+        <v>0.384971022605896</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -11409,7 +11397,7 @@
         <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.1589981764554977</v>
+        <v>-0.2441778182983398</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -11433,7 +11421,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>-1.062645554542542</v>
+        <v>0.1988919675350189</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -11450,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.1750581711530685</v>
+        <v>-0.2242408096790314</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -11474,7 +11462,7 @@
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>-0.1882944107055664</v>
+        <v>0.0513254851102829</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -11491,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.1536789089441299</v>
+        <v>-0.2446912229061127</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -11515,7 +11503,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>-0.1038608402013779</v>
+        <v>0.01227885019034147</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -11532,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.1554352045059204</v>
+        <v>-0.2589441239833832</v>
       </c>
       <c r="D271" t="n">
         <v>0</v>
@@ -11556,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>-0.2779667675495148</v>
+        <v>0.005977858323603868</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -11573,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.1656409054994583</v>
+        <v>-0.2283861488103867</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -11597,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>-0.1818287968635559</v>
+        <v>0.04505778849124908</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -11614,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.1617671698331833</v>
+        <v>-0.1966714859008789</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -11638,7 +11626,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>-0.1803814023733139</v>
+        <v>0.03635219112038612</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -11655,7 +11643,7 @@
         <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.3499516248703003</v>
+        <v>-0.2529308199882507</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -11679,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0.2396985739469528</v>
+        <v>0.1025449708104134</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -11696,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.3691852390766144</v>
+        <v>-0.2212775945663452</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -11720,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>-0.2565301954746246</v>
+        <v>0.3263994455337524</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -11737,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.3415942192077637</v>
+        <v>-0.251826673746109</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -11761,7 +11749,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>-0.9794725179672241</v>
+        <v>0.3173840045928955</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -11778,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.2390951216220856</v>
+        <v>-0.2700462937355042</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -11802,7 +11790,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>-0.8372077345848083</v>
+        <v>0.176081970334053</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -11819,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.2387737482786179</v>
+        <v>-0.2820325493812561</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -11843,7 +11831,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>-0.1170616671442986</v>
+        <v>0.1128709018230438</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -11860,7 +11848,7 @@
         <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.2717415988445282</v>
+        <v>-0.2868207395076752</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -11884,7 +11872,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>-0.04315148666501045</v>
+        <v>0.1441765576601028</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -11901,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.3164175450801849</v>
+        <v>-0.2805811166763306</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -11925,7 +11913,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>-0.3322595357894897</v>
+        <v>0.1533381044864655</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -11942,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.3565594255924225</v>
+        <v>-0.2598410546779633</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -11966,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>-0.1979294717311859</v>
+        <v>0.2392343133687973</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -11983,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.3671748340129852</v>
+        <v>-0.2216933071613312</v>
       </c>
       <c r="D282" t="n">
         <v>0</v>
@@ -12007,7 +11995,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>-0.5890598297119141</v>
+        <v>0.3299083113670349</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -12024,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.3613131642341614</v>
+        <v>-0.1229158118367195</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -12048,7 +12036,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>-0.1597785651683807</v>
+        <v>0.4805795252323151</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -12065,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.5150083899497986</v>
+        <v>-0.2068516612052917</v>
       </c>
       <c r="D284" t="n">
         <v>0</v>
@@ -12089,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>-0.4261654019355774</v>
+        <v>-0.2259676307439804</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -12106,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.5020230412483215</v>
+        <v>-0.1671964228153229</v>
       </c>
       <c r="D285" t="n">
         <v>0</v>
@@ -12130,7 +12118,7 @@
         <v>0</v>
       </c>
       <c r="K285" t="n">
-        <v>-1.829020619392395</v>
+        <v>0.2472462952136993</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -12147,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.4815325736999512</v>
+        <v>-0.1861251145601273</v>
       </c>
       <c r="D286" t="n">
         <v>0</v>
@@ -12171,7 +12159,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>-1.030590772628784</v>
+        <v>0.339795857667923</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -12188,7 +12176,7 @@
         <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.4834703505039215</v>
+        <v>-0.2707670032978058</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -12212,7 +12200,7 @@
         <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>-1.269204378128052</v>
+        <v>0.2534376978874207</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -12229,7 +12217,7 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.5220633745193481</v>
+        <v>-0.222088947892189</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -12253,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>-0.1617262959480286</v>
+        <v>0.1818668991327286</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -12270,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.5090750455856323</v>
+        <v>-0.1114491969347</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -12294,7 +12282,7 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>-1.151329755783081</v>
+        <v>0.4824264347553253</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -12311,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.5000693202018738</v>
+        <v>-0.1702633947134018</v>
       </c>
       <c r="D290" t="n">
         <v>0</v>
@@ -12335,7 +12323,7 @@
         <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>-1.134654641151428</v>
+        <v>0.4251473546028137</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -12352,7 +12340,7 @@
         <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.4879054725170135</v>
+        <v>-0.1266292482614517</v>
       </c>
       <c r="D291" t="n">
         <v>0</v>
@@ -12376,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>-0.8326195478439331</v>
+        <v>0.3965626060962677</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -12393,7 +12381,7 @@
         <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.4799772202968597</v>
+        <v>-0.1764268130064011</v>
       </c>
       <c r="D292" t="n">
         <v>0</v>
@@ -12417,7 +12405,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>-1.211589097976685</v>
+        <v>0.3874625563621521</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -12434,7 +12422,7 @@
         <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.4788385033607483</v>
+        <v>-0.1599345058202744</v>
       </c>
       <c r="D293" t="n">
         <v>0</v>
@@ -12458,7 +12446,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>-0.9336463212966919</v>
+        <v>0.3188073635101318</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -12475,7 +12463,7 @@
         <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>0.3367357850074768</v>
+        <v>1.093035459518433</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
@@ -12499,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>0.2781558632850647</v>
+        <v>0.03063616529107094</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -12516,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0.3324202001094818</v>
+        <v>1.096105217933655</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -12540,7 +12528,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>0.2748067378997803</v>
+        <v>0.4125777184963226</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -12557,7 +12545,7 @@
         <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>0.3475446999073029</v>
+        <v>1.098806023597717</v>
       </c>
       <c r="D296" t="n">
         <v>0</v>
@@ -12581,7 +12569,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>0.1441830098628998</v>
+        <v>0.4171265959739685</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -12598,7 +12586,7 @@
         <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.4803207814693451</v>
+        <v>-0.1759904623031616</v>
       </c>
       <c r="D297" t="n">
         <v>0</v>
@@ -12622,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>-1.368858695030212</v>
+        <v>0.6896461248397827</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -12639,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.4779760539531708</v>
+        <v>-0.2078780084848404</v>
       </c>
       <c r="D298" t="n">
         <v>0</v>
@@ -12663,7 +12651,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>-1.76874828338623</v>
+        <v>-0.04254014790058136</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -12680,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.4800264537334442</v>
+        <v>-0.1580607742071152</v>
       </c>
       <c r="D299" t="n">
         <v>0</v>
@@ -12704,7 +12692,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
-        <v>-0.7500555515289307</v>
+        <v>0.201495885848999</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -12721,7 +12709,7 @@
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.4793383777141571</v>
+        <v>-0.1819743365049362</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -12745,7 +12733,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>-0.7257505655288696</v>
+        <v>0.3267790973186493</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -12762,7 +12750,7 @@
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.4724445641040802</v>
+        <v>-0.2851160168647766</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -12786,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="K301" t="n">
-        <v>-1.277158975601196</v>
+        <v>0.242060661315918</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -12800,40 +12788,40 @@
         <v>145.975</v>
       </c>
       <c r="B302" t="n">
-        <v>201.1555633544922</v>
+        <v>194.9266052246094</v>
       </c>
       <c r="C302" t="n">
-        <v>204.8129730224609</v>
+        <v>185.8210754394531</v>
       </c>
       <c r="D302" t="n">
-        <v>199.8925571234974</v>
+        <v>199.7732511584027</v>
       </c>
       <c r="E302" t="n">
-        <v>206.7561420426908</v>
+        <v>206.3919281724314</v>
       </c>
       <c r="F302" t="n">
-        <v>201.3787998776778</v>
+        <v>199.3144936381463</v>
       </c>
       <c r="G302" t="n">
-        <v>203.1624908447266</v>
+        <v>198.2506256103516</v>
       </c>
       <c r="H302" t="n">
-        <v>200.3844387339313</v>
+        <v>199.2746804436135</v>
       </c>
       <c r="I302" t="n">
-        <v>171.9614519419278</v>
+        <v>163.2717377059515</v>
       </c>
       <c r="J302" t="n">
-        <v>180.3915100097656</v>
+        <v>176.1794128417969</v>
       </c>
       <c r="K302" t="n">
-        <v>152.0090637207031</v>
+        <v>160.5536499023438</v>
       </c>
       <c r="L302" t="n">
-        <v>176.8880894702059</v>
+        <v>177.1438077813358</v>
       </c>
       <c r="M302" t="n">
-        <v>176.8880894702059</v>
+        <v>177.1438077813358</v>
       </c>
     </row>
     <row r="303">
@@ -12841,40 +12829,40 @@
         <v>210.69</v>
       </c>
       <c r="B303" t="n">
-        <v>201.2347869873047</v>
+        <v>194.8990936279297</v>
       </c>
       <c r="C303" t="n">
-        <v>204.9430236816406</v>
+        <v>185.7194976806641</v>
       </c>
       <c r="D303" t="n">
-        <v>199.6976409358338</v>
+        <v>200.3375382895069</v>
       </c>
       <c r="E303" t="n">
-        <v>206.1205670689654</v>
+        <v>208.1063108392808</v>
       </c>
       <c r="F303" t="n">
-        <v>201.3787998776778</v>
+        <v>200.0562376990079</v>
       </c>
       <c r="G303" t="n">
-        <v>202.6217193603516</v>
+        <v>197.3421173095703</v>
       </c>
       <c r="H303" t="n">
-        <v>199.3661580592444</v>
+        <v>198.7928950907673</v>
       </c>
       <c r="I303" t="n">
-        <v>202.0486645174487</v>
+        <v>199.6681190251403</v>
       </c>
       <c r="J303" t="n">
-        <v>198.7266845703125</v>
+        <v>195.2396697998047</v>
       </c>
       <c r="K303" t="n">
-        <v>203.9076995849609</v>
+        <v>192.3954162597656</v>
       </c>
       <c r="L303" t="n">
-        <v>200.5981606699892</v>
+        <v>201.0127613515859</v>
       </c>
       <c r="M303" t="n">
-        <v>200.5981606699892</v>
+        <v>201.0127613515859</v>
       </c>
     </row>
     <row r="304">
@@ -12882,40 +12870,40 @@
         <v>202.07</v>
       </c>
       <c r="B304" t="n">
-        <v>201.1838531494141</v>
+        <v>197.0024871826172</v>
       </c>
       <c r="C304" t="n">
-        <v>204.7999267578125</v>
+        <v>186.3274383544922</v>
       </c>
       <c r="D304" t="n">
-        <v>200.9544976289054</v>
+        <v>200.8160252300001</v>
       </c>
       <c r="E304" t="n">
-        <v>209.7450139140536</v>
+        <v>209.3233118008496</v>
       </c>
       <c r="F304" t="n">
-        <v>201.7505597998046</v>
+        <v>200.2958110512766</v>
       </c>
       <c r="G304" t="n">
-        <v>205.1060638427734</v>
+        <v>199.0724945068359</v>
       </c>
       <c r="H304" t="n">
-        <v>202.6162130931383</v>
+        <v>201.2303039825869</v>
       </c>
       <c r="I304" t="n">
-        <v>202.5405255794964</v>
+        <v>199.8397164744867</v>
       </c>
       <c r="J304" t="n">
-        <v>199.269287109375</v>
+        <v>198.8530120849609</v>
       </c>
       <c r="K304" t="n">
-        <v>205.0577697753906</v>
+        <v>193.4491729736328</v>
       </c>
       <c r="L304" t="n">
-        <v>202.2979957176018</v>
+        <v>202.4243217866547</v>
       </c>
       <c r="M304" t="n">
-        <v>202.2979957176018</v>
+        <v>202.4243217866547</v>
       </c>
     </row>
     <row r="305">
@@ -12923,40 +12911,40 @@
         <v>206.935</v>
       </c>
       <c r="B305" t="n">
-        <v>201.0621643066406</v>
+        <v>203.5517578125</v>
       </c>
       <c r="C305" t="n">
-        <v>204.5623016357422</v>
+        <v>187.9741668701172</v>
       </c>
       <c r="D305" t="n">
-        <v>204.0632634153794</v>
+        <v>203.9270416309157</v>
       </c>
       <c r="E305" t="n">
-        <v>217.9639965678451</v>
+        <v>217.5563379777398</v>
       </c>
       <c r="F305" t="n">
-        <v>202.8658073816733</v>
+        <v>200.219422433823</v>
       </c>
       <c r="G305" t="n">
-        <v>210.4384155273438</v>
+        <v>202.1004638671875</v>
       </c>
       <c r="H305" t="n">
-        <v>203.0241936401073</v>
+        <v>201.7153179810905</v>
       </c>
       <c r="I305" t="n">
-        <v>203.829412020145</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J305" t="n">
-        <v>199.5420074462891</v>
+        <v>204.1238098144531</v>
       </c>
       <c r="K305" t="n">
-        <v>204.8282623291016</v>
+        <v>195.6167907714844</v>
       </c>
       <c r="L305" t="n">
-        <v>203.0907184542637</v>
+        <v>203.1062665277657</v>
       </c>
       <c r="M305" t="n">
-        <v>203.0907184542637</v>
+        <v>203.1062665277657</v>
       </c>
     </row>
     <row r="306">
@@ -12964,40 +12952,40 @@
         <v>195.745</v>
       </c>
       <c r="B306" t="n">
-        <v>200.9809417724609</v>
+        <v>204.4677581787109</v>
       </c>
       <c r="C306" t="n">
-        <v>204.4210052490234</v>
+        <v>188.2068939208984</v>
       </c>
       <c r="D306" t="n">
-        <v>204.2646015500723</v>
+        <v>204.1329103158221</v>
       </c>
       <c r="E306" t="n">
-        <v>218.2424405654454</v>
+        <v>217.8532969535184</v>
       </c>
       <c r="F306" t="n">
-        <v>202.8658073816733</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G306" t="n">
-        <v>210.8158111572266</v>
+        <v>202.7845764160156</v>
       </c>
       <c r="H306" t="n">
-        <v>202.6553725904766</v>
+        <v>201.3460833188445</v>
       </c>
       <c r="I306" t="n">
-        <v>202.8658520571296</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J306" t="n">
-        <v>199.8783111572266</v>
+        <v>207.7318572998047</v>
       </c>
       <c r="K306" t="n">
-        <v>204.3259735107422</v>
+        <v>197.3190307617188</v>
       </c>
       <c r="L306" t="n">
-        <v>203.0907184542637</v>
+        <v>202.5328308426104</v>
       </c>
       <c r="M306" t="n">
-        <v>203.0907184542637</v>
+        <v>202.5328308426104</v>
       </c>
     </row>
     <row r="307">
@@ -13005,40 +12993,40 @@
         <v>202.99</v>
       </c>
       <c r="B307" t="n">
-        <v>200.81640625</v>
+        <v>208.1297149658203</v>
       </c>
       <c r="C307" t="n">
-        <v>204.1986236572266</v>
+        <v>188.9807434082031</v>
       </c>
       <c r="D307" t="n">
-        <v>204.9797504317769</v>
+        <v>206.1858864417673</v>
       </c>
       <c r="E307" t="n">
-        <v>219.6836195913855</v>
+        <v>223.2154933741925</v>
       </c>
       <c r="F307" t="n">
-        <v>202.8658073816733</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G307" t="n">
-        <v>212.1287231445312</v>
+        <v>203.8958435058594</v>
       </c>
       <c r="H307" t="n">
-        <v>200.7104260995818</v>
+        <v>200.4056776681668</v>
       </c>
       <c r="I307" t="n">
-        <v>199.7629678033688</v>
+        <v>200.5063879144132</v>
       </c>
       <c r="J307" t="n">
-        <v>199.8037719726562</v>
+        <v>210.2421722412109</v>
       </c>
       <c r="K307" t="n">
-        <v>204.1113586425781</v>
+        <v>198.2914123535156</v>
       </c>
       <c r="L307" t="n">
-        <v>202.3661395222146</v>
+        <v>202.3905447415662</v>
       </c>
       <c r="M307" t="n">
-        <v>202.3661395222146</v>
+        <v>202.3905447415662</v>
       </c>
     </row>
     <row r="308">
@@ -13046,40 +13034,40 @@
         <v>176.54</v>
       </c>
       <c r="B308" t="n">
-        <v>200.6253967285156</v>
+        <v>207.6901397705078</v>
       </c>
       <c r="C308" t="n">
-        <v>204.0158081054688</v>
+        <v>189.1112060546875</v>
       </c>
       <c r="D308" t="n">
-        <v>204.9043697650019</v>
+        <v>205.1181879140892</v>
       </c>
       <c r="E308" t="n">
-        <v>219.104100419914</v>
+        <v>219.7127173129687</v>
       </c>
       <c r="F308" t="n">
-        <v>201.2950486111071</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G308" t="n">
-        <v>212.0931854248047</v>
+        <v>204.9491424560547</v>
       </c>
       <c r="H308" t="n">
-        <v>200.6781598918939</v>
+        <v>199.4153865562548</v>
       </c>
       <c r="I308" t="n">
-        <v>197.6822733070316</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J308" t="n">
-        <v>199.8578796386719</v>
+        <v>211.3757934570312</v>
       </c>
       <c r="K308" t="n">
-        <v>203.8950347900391</v>
+        <v>199.0717315673828</v>
       </c>
       <c r="L308" t="n">
-        <v>201.9009125876908</v>
+        <v>201.5866622094739</v>
       </c>
       <c r="M308" t="n">
-        <v>201.9009125876908</v>
+        <v>201.5866622094739</v>
       </c>
     </row>
     <row r="309">
@@ -13087,40 +13075,40 @@
         <v>192.15</v>
       </c>
       <c r="B309" t="n">
-        <v>200.6334228515625</v>
+        <v>207.6651306152344</v>
       </c>
       <c r="C309" t="n">
-        <v>204.0309753417969</v>
+        <v>189.1128387451172</v>
       </c>
       <c r="D309" t="n">
-        <v>204.8979061233605</v>
+        <v>205.1117242724479</v>
       </c>
       <c r="E309" t="n">
-        <v>219.0940711229849</v>
+        <v>219.7028880533983</v>
       </c>
       <c r="F309" t="n">
-        <v>201.2950486111071</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G309" t="n">
-        <v>212.0518493652344</v>
+        <v>204.9414978027344</v>
       </c>
       <c r="H309" t="n">
-        <v>200.6781598918939</v>
+        <v>199.4153865562548</v>
       </c>
       <c r="I309" t="n">
-        <v>197.6822733070316</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J309" t="n">
-        <v>199.6405639648438</v>
+        <v>210.6112670898438</v>
       </c>
       <c r="K309" t="n">
-        <v>203.2203216552734</v>
+        <v>198.9183349609375</v>
       </c>
       <c r="L309" t="n">
-        <v>201.9009125876908</v>
+        <v>201.4434467762748</v>
       </c>
       <c r="M309" t="n">
-        <v>201.9009125876908</v>
+        <v>201.4434467762748</v>
       </c>
     </row>
     <row r="310">
@@ -13128,40 +13116,40 @@
         <v>199.325</v>
       </c>
       <c r="B310" t="n">
-        <v>200.9019317626953</v>
+        <v>206.7994842529297</v>
       </c>
       <c r="C310" t="n">
-        <v>204.2969207763672</v>
+        <v>188.7723236083984</v>
       </c>
       <c r="D310" t="n">
-        <v>204.8773474820311</v>
+        <v>205.331172529081</v>
       </c>
       <c r="E310" t="n">
-        <v>219.5698828801931</v>
+        <v>220.8999796799683</v>
       </c>
       <c r="F310" t="n">
-        <v>202.8658073816733</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G310" t="n">
-        <v>211.935302734375</v>
+        <v>203.6635589599609</v>
       </c>
       <c r="H310" t="n">
-        <v>200.7104260995818</v>
+        <v>200.0709337488184</v>
       </c>
       <c r="I310" t="n">
-        <v>204.4353194388003</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J310" t="n">
-        <v>199.9525604248047</v>
+        <v>210.9058227539062</v>
       </c>
       <c r="K310" t="n">
-        <v>203.4286193847656</v>
+        <v>198.8861541748047</v>
       </c>
       <c r="L310" t="n">
-        <v>201.9009125876908</v>
+        <v>201.916077967166</v>
       </c>
       <c r="M310" t="n">
-        <v>201.9009125876908</v>
+        <v>201.916077967166</v>
       </c>
     </row>
     <row r="311">
@@ -13169,40 +13157,40 @@
         <v>214.17</v>
       </c>
       <c r="B311" t="n">
-        <v>200.9493560791016</v>
+        <v>204.6503295898438</v>
       </c>
       <c r="C311" t="n">
-        <v>204.3613739013672</v>
+        <v>188.3252105712891</v>
       </c>
       <c r="D311" t="n">
-        <v>204.4472050055562</v>
+        <v>204.1117811552361</v>
       </c>
       <c r="E311" t="n">
-        <v>218.6843776636859</v>
+        <v>217.696712287376</v>
       </c>
       <c r="F311" t="n">
-        <v>202.8658073816733</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G311" t="n">
-        <v>211.2016296386719</v>
+        <v>203.0640869140625</v>
       </c>
       <c r="H311" t="n">
-        <v>202.6553725904766</v>
+        <v>201.2289653851213</v>
       </c>
       <c r="I311" t="n">
-        <v>204.4353194388003</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J311" t="n">
-        <v>199.9754486083984</v>
+        <v>208.7321472167969</v>
       </c>
       <c r="K311" t="n">
-        <v>203.7012329101562</v>
+        <v>197.9599456787109</v>
       </c>
       <c r="L311" t="n">
-        <v>202.4004491493434</v>
+        <v>202.4176053542297</v>
       </c>
       <c r="M311" t="n">
-        <v>202.4004491493434</v>
+        <v>202.4176053542297</v>
       </c>
     </row>
     <row r="312">
@@ -13210,40 +13198,40 @@
         <v>222.47</v>
       </c>
       <c r="B312" t="n">
-        <v>200.8604888916016</v>
+        <v>206.8997802734375</v>
       </c>
       <c r="C312" t="n">
-        <v>204.2591094970703</v>
+        <v>188.7525634765625</v>
       </c>
       <c r="D312" t="n">
-        <v>204.9032020485967</v>
+        <v>205.3570270956466</v>
       </c>
       <c r="E312" t="n">
-        <v>219.6101789839893</v>
+        <v>220.938577481463</v>
       </c>
       <c r="F312" t="n">
-        <v>202.8658073816733</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G312" t="n">
-        <v>211.990478515625</v>
+        <v>203.6686553955078</v>
       </c>
       <c r="H312" t="n">
-        <v>200.7104260995818</v>
+        <v>200.0709337488184</v>
       </c>
       <c r="I312" t="n">
-        <v>204.5645844106823</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J312" t="n">
-        <v>199.9369506835938</v>
+        <v>210.0069122314453</v>
       </c>
       <c r="K312" t="n">
-        <v>204.1496124267578</v>
+        <v>198.2629547119141</v>
       </c>
       <c r="L312" t="n">
-        <v>202.3661395222146</v>
+        <v>202.3690725332356</v>
       </c>
       <c r="M312" t="n">
-        <v>202.3661395222146</v>
+        <v>202.3690725332356</v>
       </c>
     </row>
     <row r="313">
@@ -13251,40 +13239,40 @@
         <v>220.715</v>
       </c>
       <c r="B313" t="n">
-        <v>200.8193054199219</v>
+        <v>208.1546936035156</v>
       </c>
       <c r="C313" t="n">
-        <v>204.1840667724609</v>
+        <v>188.9842529296875</v>
       </c>
       <c r="D313" t="n">
-        <v>204.9862140734183</v>
+        <v>206.1923500834087</v>
       </c>
       <c r="E313" t="n">
-        <v>219.693595835154</v>
+        <v>223.2243412186047</v>
       </c>
       <c r="F313" t="n">
-        <v>202.8658073816733</v>
+        <v>199.8642447597132</v>
       </c>
       <c r="G313" t="n">
-        <v>212.1458282470703</v>
+        <v>203.9026947021484</v>
       </c>
       <c r="H313" t="n">
-        <v>200.7104260995818</v>
+        <v>200.4056776681668</v>
       </c>
       <c r="I313" t="n">
-        <v>199.6337028314868</v>
+        <v>200.5063879144132</v>
       </c>
       <c r="J313" t="n">
-        <v>200.0358123779297</v>
+        <v>211.6529388427734</v>
       </c>
       <c r="K313" t="n">
-        <v>204.0146179199219</v>
+        <v>198.9674682617188</v>
       </c>
       <c r="L313" t="n">
-        <v>201.9009125876908</v>
+        <v>202.1114025524411</v>
       </c>
       <c r="M313" t="n">
-        <v>201.9009125876908</v>
+        <v>202.1114025524411</v>
       </c>
     </row>
     <row r="314">
@@ -13292,40 +13280,40 @@
         <v>192.635</v>
       </c>
       <c r="B314" t="n">
-        <v>200.3555145263672</v>
+        <v>210.1927490234375</v>
       </c>
       <c r="C314" t="n">
-        <v>203.7379455566406</v>
+        <v>189.8602600097656</v>
       </c>
       <c r="D314" t="n">
-        <v>205.4858381295435</v>
+        <v>205.6126401249801</v>
       </c>
       <c r="E314" t="n">
-        <v>219.8085608879308</v>
+        <v>220.1552732278136</v>
       </c>
       <c r="F314" t="n">
-        <v>198.1489997904914</v>
+        <v>194.3314367695895</v>
       </c>
       <c r="G314" t="n">
-        <v>213.219970703125</v>
+        <v>207.1295318603516</v>
       </c>
       <c r="H314" t="n">
-        <v>200.1534336918053</v>
+        <v>198.7418405231435</v>
       </c>
       <c r="I314" t="n">
-        <v>197.6822733070316</v>
+        <v>200.5116175112527</v>
       </c>
       <c r="J314" t="n">
-        <v>199.7206115722656</v>
+        <v>212.9503479003906</v>
       </c>
       <c r="K314" t="n">
-        <v>204.0413665771484</v>
+        <v>199.6804046630859</v>
       </c>
       <c r="L314" t="n">
-        <v>201.5857773558591</v>
+        <v>201.6201127562311</v>
       </c>
       <c r="M314" t="n">
-        <v>201.5857773558591</v>
+        <v>201.6201127562311</v>
       </c>
     </row>
     <row r="315">
@@ -13333,40 +13321,40 @@
         <v>193.565</v>
       </c>
       <c r="B315" t="n">
-        <v>199.0238647460938</v>
+        <v>209.6404876708984</v>
       </c>
       <c r="C315" t="n">
-        <v>201.5613403320312</v>
+        <v>190.2325286865234</v>
       </c>
       <c r="D315" t="n">
-        <v>205.4160152706841</v>
+        <v>206.1211435630607</v>
       </c>
       <c r="E315" t="n">
-        <v>219.5519295702914</v>
+        <v>221.391333090641</v>
       </c>
       <c r="F315" t="n">
-        <v>195.4010676128642</v>
+        <v>193.6432802786618</v>
       </c>
       <c r="G315" t="n">
-        <v>210.6286468505859</v>
+        <v>209.8544464111328</v>
       </c>
       <c r="H315" t="n">
-        <v>198.4476625010757</v>
+        <v>198.5102124426382</v>
       </c>
       <c r="I315" t="n">
-        <v>188.6242834595656</v>
+        <v>197.2017744887939</v>
       </c>
       <c r="J315" t="n">
-        <v>199.0689239501953</v>
+        <v>212.9036407470703</v>
       </c>
       <c r="K315" t="n">
-        <v>202.9847412109375</v>
+        <v>199.0010223388672</v>
       </c>
       <c r="L315" t="n">
-        <v>199.9315787249635</v>
+        <v>200.012383073959</v>
       </c>
       <c r="M315" t="n">
-        <v>199.9315787249635</v>
+        <v>200.012383073959</v>
       </c>
     </row>
   </sheetData>
